--- a/QCM5_1_PHY.xlsx
+++ b/QCM5_1_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C6166E-C808-4B99-B5FC-7EDE6E5A0702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85E4AEC3-D145-4C26-A663-FE5D223824FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="175">
   <si>
     <t>Question</t>
   </si>
@@ -447,18 +447,114 @@
     <t>Le mobile repasse par sa position d'équilibre à la date :</t>
   </si>
   <si>
-    <t>Le solide M : On considère un solide ponctuel de masse $m = 1\text{ kg}$ glissant, sans vitesse initiale, à partir du point A sur un demi-cercle vertical de rayon de $1\text{ m}$ et prolongé par une piste horizontale BC, de $2\text{ m}$ de longueur, caractérisée par une force de frottements $f = \mu \cdot R_N$ avec $\mu = 0,25$ et $R_N$ réaction normale entre le support et le solide. Le solide M continue son trajet et percute alors un ressort de raideur $k$ qu'il comprime de $10\text{ cm}$. 
+    <t>PHY_QCM1_5_Q1.png</t>
+  </si>
+  <si>
+    <t>Situation 1 : On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates ($t = 0$). La courbe représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.</t>
+  </si>
+  <si>
+    <t>L'oscillateur mécanique : L'oscillateur mécanique étudié est constitué d'un solide (S) de centre d'inertie G et de masse $m = 200\text{ g}$ et d'un ressort à spires non jointives, de masse négligeable et de raideur $K$. Le ressort est horizontal, une de ses extrémités est fixée à un support et l'autre est accrochée au solide (S). 
+&lt;img src="/images/PHY_QCM1_5_Q2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+A l'équilibre, l'abscisse du centre d'inertie G est $x=0$. L'équation s'écrit : $x(t) = X_m \cos(\frac{2\pi}{T_0}t + \varphi)$.</t>
+  </si>
+  <si>
+    <t>Situation 2 : On écarte (S) de sa position d'équilibre, dans le sens positif, et on l'envoie à un instant de date $t = 0$ avec une vitesse initiale $v_0$. La courbe représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.</t>
+  </si>
+  <si>
+    <t>Q115. La valeur de $X_m$ vaut :</t>
+  </si>
+  <si>
+    <t>Q116. La valeur de $T_0$ vaut :</t>
+  </si>
+  <si>
+    <t>Q117. La valeur de $\varphi$ vaut :</t>
+  </si>
+  <si>
+    <t>$X_m = 5\text{ cm}$</t>
+  </si>
+  <si>
+    <t>$T_0 = 4\text{ ms}$</t>
+  </si>
+  <si>
+    <t>$T_0 = 40\text{ ms}$</t>
+  </si>
+  <si>
+    <t>$T_0 = 400\text{ ms}$</t>
+  </si>
+  <si>
+    <t>$T_0 = 4\text{ s}$</t>
+  </si>
+  <si>
+    <t>$\varphi = -\frac{\pi}{3}$</t>
+  </si>
+  <si>
+    <t>$\varphi = -\frac{\pi}{4}$</t>
+  </si>
+  <si>
+    <t>$\varphi = -\frac{\pi}{6}$</t>
+  </si>
+  <si>
+    <t>Situation 3 : On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates ($t = 0$). La courbe représente l'évolution au cours du temps de l'accélération $a_x$ du centre d'inertie G.</t>
+  </si>
+  <si>
+    <t>Q118. La valeur de $X_m$ vaut :</t>
+  </si>
+  <si>
+    <t>Q119. La valeur de $\varphi$ vaut :</t>
+  </si>
+  <si>
+    <t>$X_m = 1\text{ cm}$</t>
+  </si>
+  <si>
+    <t>$\varphi = \frac{\pi}{3}$</t>
+  </si>
+  <si>
+    <t>$\varphi = \frac{\pi}{4}$</t>
+  </si>
+  <si>
+    <t>$\varphi = \frac{\pi}{6}$</t>
+  </si>
+  <si>
+    <t>Situation 4 : On écarte (S) de sa position d'équilibre, dans le sens positif, et on l'envoie à un instant de date $t = 0$ avec une vitesse initiale $\vec{v}_0$ telle que $\vec{v}_0 = v_0\vec{i}$. La courbe représente l'évolution au cours du temps de la vitesse $v_x$ du centre d'inertie G.</t>
+  </si>
+  <si>
+    <t>Q120. La valeur de $K$ vaut :</t>
+  </si>
+  <si>
+    <t>Q121. La valeur de $X_m$ vaut :</t>
+  </si>
+  <si>
+    <t>Q122. La valeur de $\varphi$ vaut :</t>
+  </si>
+  <si>
+    <t>$K = 0,05\text{ N.m}^{-1}$</t>
+  </si>
+  <si>
+    <t>$K = 0,5\text{ N.m}^{-1}$</t>
+  </si>
+  <si>
+    <t>$K = 5\text{ N.m}^{-1}$</t>
+  </si>
+  <si>
+    <t>$K = 50\text{ N.m}^{-1}$</t>
+  </si>
+  <si>
+    <t>$X_m = 2,1\text{ cm}$</t>
+  </si>
+  <si>
+    <t>$X_m = 4,2\text{ cm}$</t>
+  </si>
+  <si>
+    <t>$X_m = 5,1\text{ cm}$</t>
+  </si>
+  <si>
+    <t>$X_m = 6,2\text{ cm}$</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;&lt;center&gt;Le solide M&lt;/center&gt;&lt;/b&gt;
+&lt;br&gt; On considère un solide ponctuel de masse $m = 1\text{ kg}$ glissant, sans vitesse initiale, à partir du point A sur un demi-cercle vertical de rayon de $1\text{ m}$ et prolongé par une piste horizontale BC, de $2\text{ m}$ de longueur, caractérisée par une force de frottements $f = \mu \cdot R_N$ avec $\mu = 0,25$ et $R_N$ réaction normale entre le support et le solide. Le solide M continue son trajet et percute alors un ressort de raideur $k$ qu'il comprime de $10\text{ cm}$. 
 &lt;img src="/images/PHY_QCM1_5_Q1.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
 On donne $g = 10\text{ m.s}^{-2}$ ; $\sqrt{10} = 3,15$.</t>
-  </si>
-  <si>
-    <t>L'oscillateur mécanique : L'oscillateur mécanique étudié est constitué d'un solide (S) de centre d'inertie G et de masse $m = 200\text{ g}$ et d'un ressort à spires non jointives, de masse négligeable et de raideur $K$. Le ressort est horizontal, une de ses extrémités est fixée à un support et l'autre est accrochée au solide (S). 
-&lt;img src="/images/PHY_QCM1_5_Q2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
-A l'équilibre, l'abscisse du centre d'inertie G est $x=0$. L'équation s'écrit : $x(t) = X_m \cos(\frac{2\pi}{T_0}t + \varphi)$.
-&lt;br&gt; Situation 1 : On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant $t=0$.</t>
-  </si>
-  <si>
-    <t>PHY_QCM1_5_Q1.png</t>
   </si>
 </sst>
 </file>
@@ -936,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52.28515625" customWidth="1"/>
@@ -1123,7 +1219,7 @@
     </row>
     <row r="7" spans="1:11" ht="191.25" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>120</v>
@@ -1148,7 +1244,7 @@
         <v>34</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="K7" s="7"/>
     </row>
@@ -1233,433 +1329,646 @@
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
     </row>
-    <row r="11" spans="1:11" ht="191.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="153" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14" t="s">
-        <v>51</v>
+        <v>142</v>
       </c>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="11" t="s">
+    <row r="12" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="12" t="s">
+      <c r="C13" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E13" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F13" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G13" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12" t="s">
+      <c r="H13" s="12"/>
+      <c r="I13" s="12" t="s">
         <v>54</v>
-      </c>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14" t="s">
-        <v>60</v>
       </c>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
     </row>
-    <row r="14" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="11" t="s">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="8"/>
+      <c r="B14" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+    </row>
+    <row r="15" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="12" t="s">
+      <c r="C15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E15" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F15" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G15" s="12" t="s">
         <v>65</v>
-      </c>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="127.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="G15" s="12" t="s">
-        <v>69</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="13" t="s">
-        <v>129</v>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>144</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="11" t="s">
-        <v>130</v>
+      <c r="D16" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="10"/>
+      <c r="B17" s="13" t="s">
+        <v>145</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="10"/>
+      <c r="B18" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="E19" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="F19" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F17" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="G17" s="12" t="s">
+      <c r="G19" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B18" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="F18" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="G18" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="102" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="G19" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="H19" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="I19" s="14" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="11" t="s">
-        <v>133</v>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="10"/>
+      <c r="B20" s="13" t="s">
+        <v>157</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D20" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="G20" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="D20" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="H20" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>162</v>
+      </c>
       <c r="B21" s="13" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>88</v>
+        <v>166</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>89</v>
+        <v>167</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>90</v>
+        <v>168</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>91</v>
+        <v>169</v>
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="14" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="10"/>
       <c r="B22" s="11" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>92</v>
+        <v>170</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>93</v>
+        <v>171</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>83</v>
+        <v>172</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>84</v>
+        <v>173</v>
       </c>
       <c r="H22" s="12"/>
       <c r="I22" s="12" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="10"/>
+      <c r="B23" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="127.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B25" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B26" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B27" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="G27" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="102" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="F28" s="14" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" ht="140.25" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
+      <c r="G28" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="H28" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="I28" s="14" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B29" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B30" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B31" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="140.25" x14ac:dyDescent="0.25">
+      <c r="A32" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B32" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="12" t="s">
+      <c r="C32" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="E32" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F23" s="12" t="s">
+      <c r="F32" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="G23" s="12" t="s">
+      <c r="G32" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12" t="s">
+      <c r="H32" s="12"/>
+      <c r="I32" s="12" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B24" s="13" t="s">
+    <row r="33" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B33" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="14" t="s">
+      <c r="C33" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E33" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="F33" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="G24" s="14" t="s">
+      <c r="G33" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14" t="s">
+      <c r="H33" s="14"/>
+      <c r="I33" s="14" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B25" s="11" t="s">
+    <row r="34" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B34" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="12" t="s">
+      <c r="C34" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E34" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="F25" s="12" t="s">
+      <c r="F34" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="G25" s="12" t="s">
+      <c r="G34" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12" t="s">
+      <c r="H34" s="12"/>
+      <c r="I34" s="12" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B26" s="13" t="s">
+    <row r="35" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B35" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="14" t="s">
+      <c r="C35" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E35" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F35" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="G26" s="14" t="s">
+      <c r="G35" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14" t="s">
+      <c r="H35" s="14"/>
+      <c r="I35" s="14" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B27" s="11" t="s">
+    <row r="36" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B36" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="12" t="s">
+      <c r="C36" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="E27" s="12" t="s">
+      <c r="E36" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="F27" s="12" t="s">
+      <c r="F36" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="G27" s="12" t="s">
+      <c r="G36" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12" t="s">
+      <c r="H36" s="12"/>
+      <c r="I36" s="12" t="s">
         <v>111</v>
       </c>
     </row>

--- a/QCM5_1_PHY.xlsx
+++ b/QCM5_1_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85E4AEC3-D145-4C26-A663-FE5D223824FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADDDC8A-7A5C-448C-80C2-A90644DD4F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="175">
   <si>
     <t>Question</t>
   </si>
@@ -1333,6 +1333,9 @@
       <c r="A11" s="10" t="s">
         <v>142</v>
       </c>
+      <c r="C11" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
     </row>

--- a/QCM5_1_PHY.xlsx
+++ b/QCM5_1_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADDDC8A-7A5C-448C-80C2-A90644DD4F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6731334C-14EA-4700-A7FF-C39032F412D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="166">
   <si>
     <t>Question</t>
   </si>
@@ -450,26 +450,9 @@
     <t>PHY_QCM1_5_Q1.png</t>
   </si>
   <si>
-    <t>Situation 1 : On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates ($t = 0$). La courbe représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.</t>
-  </si>
-  <si>
-    <t>L'oscillateur mécanique : L'oscillateur mécanique étudié est constitué d'un solide (S) de centre d'inertie G et de masse $m = 200\text{ g}$ et d'un ressort à spires non jointives, de masse négligeable et de raideur $K$. Le ressort est horizontal, une de ses extrémités est fixée à un support et l'autre est accrochée au solide (S). 
-&lt;img src="/images/PHY_QCM1_5_Q2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
-A l'équilibre, l'abscisse du centre d'inertie G est $x=0$. L'équation s'écrit : $x(t) = X_m \cos(\frac{2\pi}{T_0}t + \varphi)$.</t>
-  </si>
-  <si>
     <t>Situation 2 : On écarte (S) de sa position d'équilibre, dans le sens positif, et on l'envoie à un instant de date $t = 0$ avec une vitesse initiale $v_0$. La courbe représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.</t>
   </si>
   <si>
-    <t>Q115. La valeur de $X_m$ vaut :</t>
-  </si>
-  <si>
-    <t>Q116. La valeur de $T_0$ vaut :</t>
-  </si>
-  <si>
-    <t>Q117. La valeur de $\varphi$ vaut :</t>
-  </si>
-  <si>
     <t>$X_m = 5\text{ cm}$</t>
   </si>
   <si>
@@ -497,12 +480,6 @@
     <t>Situation 3 : On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates ($t = 0$). La courbe représente l'évolution au cours du temps de l'accélération $a_x$ du centre d'inertie G.</t>
   </si>
   <si>
-    <t>Q118. La valeur de $X_m$ vaut :</t>
-  </si>
-  <si>
-    <t>Q119. La valeur de $\varphi$ vaut :</t>
-  </si>
-  <si>
     <t>$X_m = 1\text{ cm}$</t>
   </si>
   <si>
@@ -516,15 +493,6 @@
   </si>
   <si>
     <t>Situation 4 : On écarte (S) de sa position d'équilibre, dans le sens positif, et on l'envoie à un instant de date $t = 0$ avec une vitesse initiale $\vec{v}_0$ telle que $\vec{v}_0 = v_0\vec{i}$. La courbe représente l'évolution au cours du temps de la vitesse $v_x$ du centre d'inertie G.</t>
-  </si>
-  <si>
-    <t>Q120. La valeur de $K$ vaut :</t>
-  </si>
-  <si>
-    <t>Q121. La valeur de $X_m$ vaut :</t>
-  </si>
-  <si>
-    <t>Q122. La valeur de $\varphi$ vaut :</t>
   </si>
   <si>
     <t>$K = 0,05\text{ N.m}^{-1}$</t>
@@ -555,6 +523,12 @@
 &lt;br&gt; On considère un solide ponctuel de masse $m = 1\text{ kg}$ glissant, sans vitesse initiale, à partir du point A sur un demi-cercle vertical de rayon de $1\text{ m}$ et prolongé par une piste horizontale BC, de $2\text{ m}$ de longueur, caractérisée par une force de frottements $f = \mu \cdot R_N$ avec $\mu = 0,25$ et $R_N$ réaction normale entre le support et le solide. Le solide M continue son trajet et percute alors un ressort de raideur $k$ qu'il comprime de $10\text{ cm}$. 
 &lt;img src="/images/PHY_QCM1_5_Q1.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
 On donne $g = 10\text{ m.s}^{-2}$ ; $\sqrt{10} = 3,15$.</t>
+  </si>
+  <si>
+    <t>L'oscillateur mécanique : L'oscillateur mécanique étudié est constitué d'un solide (S) de centre d'inertie G et de masse $m = 200\text{ g}$ et d'un ressort à spires non jointives, de masse négligeable et de raideur $K$. Le ressort est horizontal, une de ses extrémités est fixée à un support et l'autre est accrochée au solide (S). 
+&lt;img src="/images/PHY_QCM1_5_Q2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+A l'équilibre, l'abscisse du centre d'inertie G est $x=0$. L'équation s'écrit : $x(t) = X_m \cos(\frac{2\pi}{T_0}t + \varphi)$.
+&lt;br&gt; Situation 1 : On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates ($t = 0$). La courbe représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.</t>
   </si>
 </sst>
 </file>
@@ -1032,7 +1006,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52.28515625" customWidth="1"/>
@@ -1219,7 +1193,7 @@
     </row>
     <row r="7" spans="1:11" ht="191.25" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>120</v>
@@ -1329,649 +1303,641 @@
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
     </row>
-    <row r="11" spans="1:11" ht="153" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="216.75" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>142</v>
+        <v>165</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>124</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>3</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14" t="s">
+        <v>51</v>
       </c>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>124</v>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="11" t="s">
+        <v>125</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14" t="s">
-        <v>51</v>
-      </c>
+      <c r="D12" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="11" t="s">
-        <v>125</v>
+      <c r="A13" s="8"/>
+      <c r="B13" s="13" t="s">
+        <v>126</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12" t="s">
-        <v>54</v>
+      <c r="D13" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14" t="s">
+        <v>60</v>
       </c>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="13" t="s">
-        <v>126</v>
+    <row r="14" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="11" t="s">
+        <v>127</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-    </row>
-    <row r="15" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="D14" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>141</v>
+      </c>
       <c r="B15" s="11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>65</v>
+        <v>142</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="12" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="10"/>
+      <c r="B16" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="E16" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12" t="s">
-        <v>75</v>
+      <c r="F16" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10"/>
-      <c r="B17" s="13" t="s">
-        <v>145</v>
+      <c r="B17" s="11" t="s">
+        <v>126</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="F17" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="G17" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="H17" s="12"/>
+      <c r="I17" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="G17" s="14" t="s">
+      <c r="B18" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10"/>
-      <c r="B18" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>61</v>
-      </c>
       <c r="E18" s="12" t="s">
-        <v>152</v>
+        <v>74</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="H18" s="12"/>
       <c r="I18" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="10"/>
+      <c r="B19" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19" s="14" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
+      <c r="F19" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="H19" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B20" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="12" t="s">
+      <c r="E20" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="F20" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="E19" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="G19" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10"/>
-      <c r="B20" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20" s="14" t="s">
+      <c r="G20" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="H20" s="14"/>
+      <c r="I20" s="14" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="10"/>
+      <c r="B21" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G20" s="14" t="s">
+      <c r="E21" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="H20" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="I20" s="14" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
+      <c r="F21" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="G21" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="F21" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14" t="s">
-        <v>168</v>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10"/>
-      <c r="B22" s="11" t="s">
-        <v>164</v>
+      <c r="B22" s="13" t="s">
+        <v>126</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D22" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="G22" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="10"/>
-      <c r="B23" s="13" t="s">
-        <v>165</v>
+      <c r="D22" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="127.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>128</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D23" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F23" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="127.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>128</v>
+      <c r="D23" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B24" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D24" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12" t="s">
-        <v>67</v>
+      <c r="D24" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B25" s="13" t="s">
-        <v>129</v>
+      <c r="B25" s="11" t="s">
+        <v>130</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D25" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="G25" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B26" s="11" t="s">
-        <v>130</v>
+      <c r="D25" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B26" s="13" t="s">
+        <v>131</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D26" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="G26" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="D26" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="102" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
+        <v>81</v>
+      </c>
       <c r="B27" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="H27" s="14"/>
+        <v>85</v>
+      </c>
+      <c r="H27" s="14" t="s">
+        <v>114</v>
+      </c>
       <c r="I27" s="14" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="102" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>132</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B28" s="11" t="s">
+        <v>133</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G28" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="H28" s="12"/>
+      <c r="I28" s="12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B29" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="G29" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B30" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F30" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F28" s="14" t="s">
+      <c r="G30" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="G28" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="H28" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="I28" s="14" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="G29" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B30" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="F30" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="H30" s="12"/>
+      <c r="I30" s="12" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="140.25" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
+        <v>94</v>
+      </c>
       <c r="B31" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="H31" s="12"/>
       <c r="I31" s="12" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="140.25" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>136</v>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B32" s="13" t="s">
+        <v>134</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D32" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="F32" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="G32" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12" t="s">
-        <v>96</v>
+      <c r="D32" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B33" s="13" t="s">
-        <v>134</v>
+      <c r="B33" s="11" t="s">
+        <v>137</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D33" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="E33" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="F33" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="G33" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14" t="s">
-        <v>91</v>
+      <c r="D33" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B34" s="11" t="s">
-        <v>137</v>
+      <c r="B34" s="13" t="s">
+        <v>138</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D34" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="E34" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="F34" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="G34" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12" t="s">
-        <v>102</v>
+      <c r="D34" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B35" s="13" t="s">
-        <v>138</v>
+      <c r="B35" s="11" t="s">
+        <v>139</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D35" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="E35" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="F35" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="G35" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="36" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B36" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="12" t="s">
+      <c r="D35" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="E36" s="12" t="s">
+      <c r="E35" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="F36" s="12" t="s">
+      <c r="F35" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="G36" s="12" t="s">
+      <c r="G35" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12" t="s">
+      <c r="H35" s="12"/>
+      <c r="I35" s="12" t="s">
         <v>111</v>
       </c>
     </row>

--- a/QCM5_1_PHY.xlsx
+++ b/QCM5_1_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6731334C-14EA-4700-A7FF-C39032F412D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAA933C4-4F8E-4CA6-805E-530A59B3C0DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="167">
   <si>
     <t>Question</t>
   </si>
@@ -225,9 +225,6 @@
     <t>$\frac{\pi}{25}$</t>
   </si>
   <si>
-    <t>Étude d'un système oscillant : Le solide (S) de masse $m = 200\text{ g}$ est fixé à un ressort horizontal à spires non jointives, de masse négligeable et de raideur $K$. A l'équilibre, G coïncide avec l'origine. On écarte (S) dans le sens positif d'une distance $X_m$ et on l'abandonne sans vitesse initiale à $t_0 = 0$. Le solide effectue $20$ oscillations pendant $\Delta t = 12,6\text{ s}$. On donne : $(12,6)^2 \approx 160 ; \pi^2 = 10 ; \sqrt{3} \approx 1,73$.</t>
-  </si>
-  <si>
     <t>$K = 20\text{ N.m}^{-1}$</t>
   </si>
   <si>
@@ -270,9 +267,6 @@
     <t>$x_1 = 5,19\text{ cm}$</t>
   </si>
   <si>
-    <t>Un pendule élastique : Une masse $m = 25\text{ g}$ est attachée à l'extrémité d'un ressort horizontal, de constante de raideur $k = 0,2\text{ N.m}^{-1}$ et de longueur à vide $L_0 = 10\text{ cm}$. L'autre extrémité est fixée à un point fixe O. A est le point d'abscisse $OA = 12\text{ cm}$ et B est le point d'abscisse $OB = 8\text{ cm}$. On lâche $m$ de A avec une vitesse nulle.</t>
-  </si>
-  <si>
     <t>$0,04\text{ mJ}$</t>
   </si>
   <si>
@@ -309,9 +303,6 @@
     <t>$2 \cdot 10^{-4}\text{ J}$</t>
   </si>
   <si>
-    <t>Une tige horizontale : Soit le pendule élastique constitué d'un cylindre de masse $m = 200\text{ g}$ attachée à un ressort dont la constante de raideur est $k = 20\text{ N.m}^{-1}$. On donne : $2\pi \approx 6,3 ; \sqrt{10} = 3,2 ; 6,3 \times 3,2 = 20$. L'ensemble peut coulisser sans frottements. A l'équilibre, son centre d'inertie coïncide avec l'origine de l'axe O. On écarte le solide de sa position d'équilibre d'une distance $x = 2,0\text{ cm}$ puis on le lance avec une vitesse $v_{0x} = 0,20\text{ m.s}^{-1}$.</t>
-  </si>
-  <si>
     <t>$6,3\text{ s}$</t>
   </si>
   <si>
@@ -450,9 +441,6 @@
     <t>PHY_QCM1_5_Q1.png</t>
   </si>
   <si>
-    <t>Situation 2 : On écarte (S) de sa position d'équilibre, dans le sens positif, et on l'envoie à un instant de date $t = 0$ avec une vitesse initiale $v_0$. La courbe représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.</t>
-  </si>
-  <si>
     <t>$X_m = 5\text{ cm}$</t>
   </si>
   <si>
@@ -477,9 +465,6 @@
     <t>$\varphi = -\frac{\pi}{6}$</t>
   </si>
   <si>
-    <t>Situation 3 : On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates ($t = 0$). La courbe représente l'évolution au cours du temps de l'accélération $a_x$ du centre d'inertie G.</t>
-  </si>
-  <si>
     <t>$X_m = 1\text{ cm}$</t>
   </si>
   <si>
@@ -490,9 +475,6 @@
   </si>
   <si>
     <t>$\varphi = \frac{\pi}{6}$</t>
-  </si>
-  <si>
-    <t>Situation 4 : On écarte (S) de sa position d'équilibre, dans le sens positif, et on l'envoie à un instant de date $t = 0$ avec une vitesse initiale $\vec{v}_0$ telle que $\vec{v}_0 = v_0\vec{i}$. La courbe représente l'évolution au cours du temps de la vitesse $v_x$ du centre d'inertie G.</t>
   </si>
   <si>
     <t>$K = 0,05\text{ N.m}^{-1}$</t>
@@ -525,10 +507,50 @@
 On donne $g = 10\text{ m.s}^{-2}$ ; $\sqrt{10} = 3,15$.</t>
   </si>
   <si>
-    <t>L'oscillateur mécanique : L'oscillateur mécanique étudié est constitué d'un solide (S) de centre d'inertie G et de masse $m = 200\text{ g}$ et d'un ressort à spires non jointives, de masse négligeable et de raideur $K$. Le ressort est horizontal, une de ses extrémités est fixée à un support et l'autre est accrochée au solide (S). 
-&lt;img src="/images/PHY_QCM1_5_Q2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
-A l'équilibre, l'abscisse du centre d'inertie G est $x=0$. L'équation s'écrit : $x(t) = X_m \cos(\frac{2\pi}{T_0}t + \varphi)$.
-&lt;br&gt; Situation 1 : On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates ($t = 0$). La courbe représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.</t>
+    <t>L'oscillateur mécanique étudié est constitué d'un solide (S) de centre d'inertie G et de masse $m = 200\text{ g}$ et d'un ressort à spires non jointives, de masse négligeable et de raideur $K$. Le ressort est horizontal, une de ses extrémités est fixée à un support et l'autre extrémité est accrochée au solide (S). Ce solide peut glisser sur le plan horizontal. On étudie le mouvement du centre d'inertie G dans un repère $R(O, \vec{i})$ lié à un référentiel terrestre considéré galiléen. On repère la position du centre d'inertie G, à un instant $t$, par l'abscisse $x$ sur l'axe $Ox$. À l'équilibre, l'abscisse du centre d'inertie G est $x_e = 0$. On prendra $\pi^2 = 10$. La solution de l'équation différentielle s'écrit sous la forme : $x(t) = X_m \cos\left(\frac{2\pi}{T_0}t + \varphi\right)$.
+&lt;br&gt;&lt;br&gt;&lt;b&gt; Situation 1 : &lt;/b&gt;
+&lt;br&gt;On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates ($t = 0$). 
+La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.
+&lt;img src="/images/PHY_QCM1_5_Q2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Situation 2 :&lt;/b&gt;
+ On écarte (S) de sa position d'équilibre, dans le sens positif, et on l'envoie à un instant de date $t = 0$ avec une vitesse initiale $v_0$. 
+La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.
+&lt;img src="/images/PHY_QCM1_5_Q3.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Situation 3 :&lt;/b&gt; 
+On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates ($t = 0$). 
+La courbe de la figure suivante représente l'évolution au cours du temps de l'accélération $a_x$ du centre d'inertie G.
+&lt;img src="/images/PHY_QCM1_5_Q4.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Situation 4 :&lt;/b&gt; 
+On écarte (S) de sa position d'équilibre, dans le sens positif, et on l'envoie à un instant de date $t = 0$ avec une vitesse initiale $\vec{v}_0$ telle que $\vec{v}_0 = v_0\vec{i}$. 
+La courbe de la figure suivante représente l'évolution au cours du temps de la vitesse $v_x$ du centre d'inertie G.
+&lt;img src="/images/PHY_QCM1_5_Q5.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+  </si>
+  <si>
+    <t>&lt;br&gt;&lt;center&gt;Étude d'un système oscillant&lt;/center&gt;&lt;/br&gt; 
+Le solide (S) de masse $m = 200\text{ g}$ est fixé à un ressort horizontal à spires non jointives, de masse négligeable et de raideur $K$. A l'équilibre, le centre d'inertie G coïncide avec l'origine du repère $(O, \vec{i})$ lié à un référentiel terrestre considéré galiléen (Figure 2). 
+&lt;img src="/images/PHY_QCM1_6_Q2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+On écarte (S) dans le sens positif d'une distance $X_m$ et on l'abandonne sans vitesse initiale à $t_0 = 0$. Le solide effectue $20$ oscillations pendant $\Delta t = 12,6\text{ s}$. On donne : $(12,6)^2 \approx 160 ; \pi^2 = 10 ; \sqrt{3} \approx 1,73$.</t>
+  </si>
+  <si>
+    <t>&lt;br&gt;&lt;center&gt;Un pendule élastique &lt;/center&gt;&lt;/br&gt;
+Une masse $m = 25\text{ g}$ est attachée à l'extrémité d'un ressort horizontal, de constante de raideur $k = 0,2\text{ N.m}^{-1}$ et de longueur à vide $L_0 = 10\text{ cm}$. L'autre extrémité est fixée à un point fixe O. A est le point d'abscisse $OA = 12\text{ cm}$ et B est le point d'abscisse $OB = 8\text{ cm}$. On lâche $m$ de A avec une vitesse nulle.
+&lt;img src="/images/PHY_QCM1_7_Q2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;br&gt;&lt;center&gt;Une tige horizontale &lt;/center&gt;&lt;/br&gt;
+ Soit le pendule élastique constitué d'un cylindre de masse $m = 200\text{ g}$ attachée à un ressort dont la constante de raideur est $k = 20\text{ N.m}^{-1}$. On donne : $2\pi \approx 6,3 ; \sqrt{10} = 3,2 ; 6,3 \times 3,2 = 20$. On considère que l'ensemble peut coulisser sans frottements sur une tige horizontale. Lorsque le cylindre est en équilibre, son centre d'inertie coïncide avec la graduation O de l'axe.
+&lt;img src="/images/PHY_QCM1_8_Q2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> On écarte le solide de sa position d'équilibre d'une distance $x = 2,0\text{ cm}$ puis on le lance avec une vitesse $v_{0x} = 0,20\text{ m.s}^{-1}$.
+&lt;b&gt;La pulsation du mouvement vaut :</t>
   </si>
 </sst>
 </file>
@@ -570,7 +592,7 @@
       <name val="Consolas"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -593,6 +615,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFE9EFF7"/>
         <bgColor rgb="FFE9EFF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+        <bgColor rgb="FFDCE6F1"/>
       </patternFill>
     </fill>
   </fills>
@@ -662,7 +690,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -703,6 +731,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1057,7 +1088,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>3</v>
@@ -1084,7 +1115,7 @@
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
       <c r="B3" s="13" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>3</v>
@@ -1113,7 +1144,7 @@
         <v>21</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>3</v>
@@ -1140,7 +1171,7 @@
     <row r="5" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="8"/>
       <c r="B5" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>3</v>
@@ -1167,7 +1198,7 @@
     <row r="6" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="13" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>3</v>
@@ -1193,10 +1224,10 @@
     </row>
     <row r="7" spans="1:11" ht="191.25" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>3</v>
@@ -1218,14 +1249,14 @@
         <v>34</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="K7" s="7"/>
     </row>
     <row r="8" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
       <c r="B8" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>3</v>
@@ -1252,7 +1283,7 @@
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
       <c r="B9" s="13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>3</v>
@@ -1279,7 +1310,7 @@
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="11" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>3</v>
@@ -1303,12 +1334,12 @@
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
     </row>
-    <row r="11" spans="1:11" ht="216.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>165</v>
+    <row r="11" spans="1:11" ht="331.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
+        <v>159</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>3</v>
@@ -1335,7 +1366,7 @@
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="11" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>3</v>
@@ -1362,7 +1393,7 @@
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>3</v>
@@ -1388,7 +1419,7 @@
     </row>
     <row r="14" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>3</v>
@@ -1412,60 +1443,60 @@
     </row>
     <row r="15" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E15" s="12" t="s">
         <v>51</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10"/>
       <c r="B16" s="13" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="H16" s="14"/>
       <c r="I16" s="14" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10"/>
       <c r="B17" s="11" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>3</v>
@@ -1474,50 +1505,50 @@
         <v>61</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17" s="12" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E18" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="F18" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="G18" s="12" t="s">
         <v>75</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>76</v>
       </c>
       <c r="H18" s="12"/>
       <c r="I18" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10"/>
       <c r="B19" s="13" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>3</v>
@@ -1526,13 +1557,13 @@
         <v>58</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="H19" s="14" t="s">
         <v>59</v>
@@ -1543,60 +1574,60 @@
     </row>
     <row r="20" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="H20" s="14"/>
       <c r="I20" s="14" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="12" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10"/>
       <c r="B22" s="13" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>3</v>
@@ -1605,25 +1636,25 @@
         <v>61</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="14" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="127.5" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="216.75" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>66</v>
+        <v>163</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>3</v>
@@ -1632,313 +1663,313 @@
         <v>47</v>
       </c>
       <c r="E23" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="F23" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="F23" s="12" t="s">
+      <c r="G23" s="12" t="s">
         <v>68</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>69</v>
       </c>
       <c r="H23" s="12"/>
       <c r="I23" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B24" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="F24" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="G24" s="14" t="s">
         <v>72</v>
-      </c>
-      <c r="G24" s="14" t="s">
-        <v>73</v>
       </c>
       <c r="H24" s="14"/>
       <c r="I24" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B25" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="E25" s="12" t="s">
         <v>74</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>75</v>
       </c>
       <c r="F25" s="12" t="s">
         <v>52</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B26" s="13" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E26" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="F26" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="G26" s="14" t="s">
         <v>79</v>
-      </c>
-      <c r="G26" s="14" t="s">
-        <v>80</v>
       </c>
       <c r="H26" s="14"/>
       <c r="I26" s="14" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="102" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="140.25" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E27" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="B27" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="14" t="s">
+      <c r="F27" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="G27" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="F27" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="G27" s="14" t="s">
-        <v>85</v>
-      </c>
       <c r="H27" s="14" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B28" s="11" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B29" s="13" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="F29" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="G29" s="14" t="s">
         <v>89</v>
-      </c>
-      <c r="F29" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="G29" s="14" t="s">
-        <v>91</v>
       </c>
       <c r="H29" s="14"/>
       <c r="I29" s="14" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B30" s="11" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="12" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="140.25" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F31" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B31" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="12" t="s">
+      <c r="G31" s="12" t="s">
         <v>95</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="F31" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="G31" s="12" t="s">
-        <v>98</v>
       </c>
       <c r="H31" s="12"/>
       <c r="I31" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="B32" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="E32" s="14" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B32" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="E32" s="14" t="s">
-        <v>99</v>
-      </c>
       <c r="F32" s="14" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H32" s="14"/>
       <c r="I32" s="14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B33" s="11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G33" s="12" t="s">
         <v>102</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="F33" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="G33" s="12" t="s">
-        <v>105</v>
       </c>
       <c r="H33" s="12"/>
       <c r="I33" s="12" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B34" s="13" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="G34" s="14" t="s">
         <v>106</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="F34" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="G34" s="14" t="s">
-        <v>109</v>
       </c>
       <c r="H34" s="14"/>
       <c r="I34" s="14" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B35" s="11" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="G35" s="12" t="s">
         <v>110</v>
-      </c>
-      <c r="E35" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="F35" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="G35" s="12" t="s">
-        <v>113</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/QCM5_1_PHY.xlsx
+++ b/QCM5_1_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAA933C4-4F8E-4CA6-805E-530A59B3C0DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{414567C0-203E-457C-980E-9D8FEE823DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -507,13 +507,6 @@
 On donne $g = 10\text{ m.s}^{-2}$ ; $\sqrt{10} = 3,15$.</t>
   </si>
   <si>
-    <t>L'oscillateur mécanique étudié est constitué d'un solide (S) de centre d'inertie G et de masse $m = 200\text{ g}$ et d'un ressort à spires non jointives, de masse négligeable et de raideur $K$. Le ressort est horizontal, une de ses extrémités est fixée à un support et l'autre extrémité est accrochée au solide (S). Ce solide peut glisser sur le plan horizontal. On étudie le mouvement du centre d'inertie G dans un repère $R(O, \vec{i})$ lié à un référentiel terrestre considéré galiléen. On repère la position du centre d'inertie G, à un instant $t$, par l'abscisse $x$ sur l'axe $Ox$. À l'équilibre, l'abscisse du centre d'inertie G est $x_e = 0$. On prendra $\pi^2 = 10$. La solution de l'équation différentielle s'écrit sous la forme : $x(t) = X_m \cos\left(\frac{2\pi}{T_0}t + \varphi\right)$.
-&lt;br&gt;&lt;br&gt;&lt;b&gt; Situation 1 : &lt;/b&gt;
-&lt;br&gt;On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates ($t = 0$). 
-La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.
-&lt;img src="/images/PHY_QCM1_5_Q2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
-  </si>
-  <si>
     <t>&lt;b&gt;Situation 2 :&lt;/b&gt;
  On écarte (S) de sa position d'équilibre, dans le sens positif, et on l'envoie à un instant de date $t = 0$ avec une vitesse initiale $v_0$. 
 La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.
@@ -551,6 +544,15 @@
   <si>
     <t xml:space="preserve"> On écarte le solide de sa position d'équilibre d'une distance $x = 2,0\text{ cm}$ puis on le lance avec une vitesse $v_{0x} = 0,20\text{ m.s}^{-1}$.
 &lt;b&gt;La pulsation du mouvement vaut :</t>
+  </si>
+  <si>
+    <t>L'oscillateur mécanique étudié est constitué d'un solide (S) de centre d'inertie G et de masse $m = 200\text{ g}$ et d'un ressort à spires non jointives, de masse négligeable et de raideur $K$. Le ressort est horizontal, une de ses extrémités est fixée à un support et l'autre extrémité est accrochée au solide (S). Ce solide peut glisser sur le plan horizontal. On étudie le mouvement du centre d'inertie G dans un repère $R(O, \vec{i})$ lié à un référentiel terrestre considéré galiléen. 
+&lt;b&gt;&lt;img src="/images/PHY_QCM1_5_Q2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;b&gt;On repère la position du centre d'inertie G, à un instant $t$, par l'abscisse $x$ sur l'axe $Ox$. À l'équilibre, l'abscisse du centre d'inertie G est $x_e = 0$. On prendra $\pi^2 = 10$. La solution de l'équation différentielle s'écrit sous la forme : $x(t) = X_m \cos\left(\frac{2\pi}{T_0}t + \varphi\right)$.
+&lt;br&gt;&lt;br&gt;&lt;b&gt; Situation 1 : &lt;/b&gt;
+&lt;br&gt;On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates ($t = 0$). 
+La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.
+&lt;img src="/images/PHY_QCM1_5_Q3.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
   </si>
 </sst>
 </file>
@@ -1334,9 +1336,9 @@
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
     </row>
-    <row r="11" spans="1:11" ht="331.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="357" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>121</v>
@@ -1443,7 +1445,7 @@
     </row>
     <row r="15" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>121</v>
@@ -1520,7 +1522,7 @@
     </row>
     <row r="18" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>121</v>
@@ -1574,7 +1576,7 @@
     </row>
     <row r="20" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B20" s="13" t="s">
         <v>125</v>
@@ -1651,7 +1653,7 @@
     </row>
     <row r="23" spans="1:9" ht="216.75" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>125</v>
@@ -1750,7 +1752,7 @@
     </row>
     <row r="27" spans="1:9" ht="140.25" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B27" s="13" t="s">
         <v>129</v>
@@ -1851,7 +1853,7 @@
     </row>
     <row r="31" spans="1:9" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>133</v>
@@ -1878,7 +1880,7 @@
     </row>
     <row r="32" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="B32" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>3</v>

--- a/QCM5_1_PHY.xlsx
+++ b/QCM5_1_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{414567C0-203E-457C-980E-9D8FEE823DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FACC8CBA-2DB9-400B-9311-5EFFE21A339A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -547,8 +547,8 @@
   </si>
   <si>
     <t>L'oscillateur mécanique étudié est constitué d'un solide (S) de centre d'inertie G et de masse $m = 200\text{ g}$ et d'un ressort à spires non jointives, de masse négligeable et de raideur $K$. Le ressort est horizontal, une de ses extrémités est fixée à un support et l'autre extrémité est accrochée au solide (S). Ce solide peut glisser sur le plan horizontal. On étudie le mouvement du centre d'inertie G dans un repère $R(O, \vec{i})$ lié à un référentiel terrestre considéré galiléen. 
-&lt;b&gt;&lt;img src="/images/PHY_QCM1_5_Q2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
 &lt;b&gt;On repère la position du centre d'inertie G, à un instant $t$, par l'abscisse $x$ sur l'axe $Ox$. À l'équilibre, l'abscisse du centre d'inertie G est $x_e = 0$. On prendra $\pi^2 = 10$. La solution de l'équation différentielle s'écrit sous la forme : $x(t) = X_m \cos\left(\frac{2\pi}{T_0}t + \varphi\right)$.
+&lt;br&gt;&lt;img src="/images/PHY_QCM1_5_Q2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
 &lt;br&gt;&lt;br&gt;&lt;b&gt; Situation 1 : &lt;/b&gt;
 &lt;br&gt;On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates ($t = 0$). 
 La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.

--- a/QCM5_1_PHY.xlsx
+++ b/QCM5_1_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FACC8CBA-2DB9-400B-9311-5EFFE21A339A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26FF04DD-98F4-4DE6-B10C-E1D8BA0E8AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -507,12 +507,6 @@
 On donne $g = 10\text{ m.s}^{-2}$ ; $\sqrt{10} = 3,15$.</t>
   </si>
   <si>
-    <t>&lt;b&gt;Situation 2 :&lt;/b&gt;
- On écarte (S) de sa position d'équilibre, dans le sens positif, et on l'envoie à un instant de date $t = 0$ avec une vitesse initiale $v_0$. 
-La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.
-&lt;img src="/images/PHY_QCM1_5_Q3.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
-  </si>
-  <si>
     <t>&lt;b&gt;Situation 3 :&lt;/b&gt; 
 On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates ($t = 0$). 
 La courbe de la figure suivante représente l'évolution au cours du temps de l'accélération $a_x$ du centre d'inertie G.
@@ -544,6 +538,12 @@
   <si>
     <t xml:space="preserve"> On écarte le solide de sa position d'équilibre d'une distance $x = 2,0\text{ cm}$ puis on le lance avec une vitesse $v_{0x} = 0,20\text{ m.s}^{-1}$.
 &lt;b&gt;La pulsation du mouvement vaut :</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Situation 2 :&lt;/b&gt;
+&lt;br&gt; On écarte (S) de sa position d'équilibre, dans le sens positif, et on l'envoie à un instant de date $t = 0$ avec une vitesse initiale $v_0$. 
+&lt;br&gt;La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.
+&lt;br&gt;&lt;img src="/images/PHY_QCM1_5_Q3.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
   </si>
   <si>
     <t>L'oscillateur mécanique étudié est constitué d'un solide (S) de centre d'inertie G et de masse $m = 200\text{ g}$ et d'un ressort à spires non jointives, de masse négligeable et de raideur $K$. Le ressort est horizontal, une de ses extrémités est fixée à un support et l'autre extrémité est accrochée au solide (S). Ce solide peut glisser sur le plan horizontal. On étudie le mouvement du centre d'inertie G dans un repère $R(O, \vec{i})$ lié à un référentiel terrestre considéré galiléen. 
@@ -551,8 +551,8 @@
 &lt;br&gt;&lt;img src="/images/PHY_QCM1_5_Q2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
 &lt;br&gt;&lt;br&gt;&lt;b&gt; Situation 1 : &lt;/b&gt;
 &lt;br&gt;On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates ($t = 0$). 
-La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.
-&lt;img src="/images/PHY_QCM1_5_Q3.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+&lt;br&gt;La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.
+&lt;br&gt;&lt;img src="/images/PHY_QCM1_5_Q3.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
   </si>
 </sst>
 </file>
@@ -1445,7 +1445,7 @@
     </row>
     <row r="15" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>121</v>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="18" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>121</v>
@@ -1576,7 +1576,7 @@
     </row>
     <row r="20" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B20" s="13" t="s">
         <v>125</v>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="23" spans="1:9" ht="216.75" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>125</v>
@@ -1752,7 +1752,7 @@
     </row>
     <row r="27" spans="1:9" ht="140.25" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B27" s="13" t="s">
         <v>129</v>
@@ -1853,7 +1853,7 @@
     </row>
     <row r="31" spans="1:9" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>133</v>
@@ -1880,7 +1880,7 @@
     </row>
     <row r="32" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="B32" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>3</v>

--- a/QCM5_1_PHY.xlsx
+++ b/QCM5_1_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26FF04DD-98F4-4DE6-B10C-E1D8BA0E8AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D77D46B-D85A-457B-9978-028ED94FDFB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -548,11 +548,12 @@
   <si>
     <t>L'oscillateur mécanique étudié est constitué d'un solide (S) de centre d'inertie G et de masse $m = 200\text{ g}$ et d'un ressort à spires non jointives, de masse négligeable et de raideur $K$. Le ressort est horizontal, une de ses extrémités est fixée à un support et l'autre extrémité est accrochée au solide (S). Ce solide peut glisser sur le plan horizontal. On étudie le mouvement du centre d'inertie G dans un repère $R(O, \vec{i})$ lié à un référentiel terrestre considéré galiléen. 
 &lt;b&gt;On repère la position du centre d'inertie G, à un instant $t$, par l'abscisse $x$ sur l'axe $Ox$. À l'équilibre, l'abscisse du centre d'inertie G est $x_e = 0$. On prendra $\pi^2 = 10$. La solution de l'équation différentielle s'écrit sous la forme : $x(t) = X_m \cos\left(\frac{2\pi}{T_0}t + \varphi\right)$.
-&lt;br&gt;&lt;img src="/images/PHY_QCM1_5_Q2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
-&lt;br&gt;&lt;br&gt;&lt;b&gt; Situation 1 : &lt;/b&gt;
-&lt;br&gt;On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates ($t = 0$). 
-&lt;br&gt;La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.
-&lt;br&gt;&lt;img src="/images/PHY_QCM1_5_Q3.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+&lt;img src="/images/PHY_QCM1_5_Q2.png" alt="A" class="h-20 float-right ml-4 mb-2" /&gt;
+&lt;b&gt; Situation 1 : &lt;/b&gt;&lt;br&gt;
+On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates ($t = 0$).&lt;br&gt;
+&lt;img src="/images/PHY_QCM1_5_Q3.png" alt="A" class="h-20 float-right ml-4 mb-2" /&gt;
+La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.
+&lt;div class="clear-both"&gt;&lt;/div&gt;</t>
   </si>
 </sst>
 </file>
@@ -1336,7 +1337,7 @@
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
     </row>
-    <row r="11" spans="1:11" ht="357" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="395.25" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>166</v>
       </c>

--- a/QCM5_1_PHY.xlsx
+++ b/QCM5_1_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D77D46B-D85A-457B-9978-028ED94FDFB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0066659-3785-4D04-BAEF-518BD51E2C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -550,7 +550,7 @@
 &lt;b&gt;On repère la position du centre d'inertie G, à un instant $t$, par l'abscisse $x$ sur l'axe $Ox$. À l'équilibre, l'abscisse du centre d'inertie G est $x_e = 0$. On prendra $\pi^2 = 10$. La solution de l'équation différentielle s'écrit sous la forme : $x(t) = X_m \cos\left(\frac{2\pi}{T_0}t + \varphi\right)$.
 &lt;img src="/images/PHY_QCM1_5_Q2.png" alt="A" class="h-20 float-right ml-4 mb-2" /&gt;
 &lt;b&gt; Situation 1 : &lt;/b&gt;&lt;br&gt;
-On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates ($t = 0$).&lt;br&gt;
+On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates (t = 0).&lt;br&gt;
 &lt;img src="/images/PHY_QCM1_5_Q3.png" alt="A" class="h-20 float-right ml-4 mb-2" /&gt;
 La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.
 &lt;div class="clear-both"&gt;&lt;/div&gt;</t>
@@ -1337,7 +1337,7 @@
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
     </row>
-    <row r="11" spans="1:11" ht="395.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="369.75" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>166</v>
       </c>

--- a/QCM5_1_PHY.xlsx
+++ b/QCM5_1_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0066659-3785-4D04-BAEF-518BD51E2C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA30024-7A86-4355-8519-1510A9D55BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="167">
   <si>
     <t>Question</t>
   </si>
@@ -90,9 +90,6 @@
     <t>$T = 20\text{ ms}$</t>
   </si>
   <si>
-    <t>On écarte le solide de sa position d'équilibre telle que $x = 2\text{ cm}$ puis on le lâche sans vitesse initiale.</t>
-  </si>
-  <si>
     <t>$F = 0,1\text{ N}$</t>
   </si>
   <si>
@@ -367,9 +364,6 @@
   </si>
   <si>
     <t>La période des oscillations est :</t>
-  </si>
-  <si>
-    <t>À l'abscisse $x = -2\text{ cm}$, la tension $F$ du ressort vaut :</t>
   </si>
   <si>
     <t>À un instant $t$, $x(t) = 1\text{ cm}$. L'énergie cinétique a alors pour valeur :</t>
@@ -507,18 +501,6 @@
 On donne $g = 10\text{ m.s}^{-2}$ ; $\sqrt{10} = 3,15$.</t>
   </si>
   <si>
-    <t>&lt;b&gt;Situation 3 :&lt;/b&gt; 
-On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates ($t = 0$). 
-La courbe de la figure suivante représente l'évolution au cours du temps de l'accélération $a_x$ du centre d'inertie G.
-&lt;img src="/images/PHY_QCM1_5_Q4.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Situation 4 :&lt;/b&gt; 
-On écarte (S) de sa position d'équilibre, dans le sens positif, et on l'envoie à un instant de date $t = 0$ avec une vitesse initiale $\vec{v}_0$ telle que $\vec{v}_0 = v_0\vec{i}$. 
-La courbe de la figure suivante représente l'évolution au cours du temps de la vitesse $v_x$ du centre d'inertie G.
-&lt;img src="/images/PHY_QCM1_5_Q5.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
-  </si>
-  <si>
     <t>&lt;br&gt;&lt;center&gt;Étude d'un système oscillant&lt;/center&gt;&lt;/br&gt; 
 Le solide (S) de masse $m = 200\text{ g}$ est fixé à un ressort horizontal à spires non jointives, de masse négligeable et de raideur $K$. A l'équilibre, le centre d'inertie G coïncide avec l'origine du repère $(O, \vec{i})$ lié à un référentiel terrestre considéré galiléen (Figure 2). 
 &lt;img src="/images/PHY_QCM1_6_Q2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
@@ -540,20 +522,43 @@
 &lt;b&gt;La pulsation du mouvement vaut :</t>
   </si>
   <si>
+    <t>On écarte le solide de sa position d'équilibre telle que $x = 2\text{ cm}$ puis on le lâche sans vitesse initiale.
+&lt;br&gt;À l'abscisse $x = -2\text{ cm}$, la tension $F$ du ressort vaut :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'oscillateur mécanique étudié est constitué d'un solide (S) de centre d'inertie G et de masse $m = 200\text{ g}$ et d'un ressort à spires non jointives, de masse négligeable et de raideur $K$. Le ressort est horizontal, une de ses extrémités est fixée à un support et l'autre extrémité est accrochée au solide (S). Ce solide peut glisser sur le plan horizontal. On étudie le mouvement du centre d'inertie G dans un repère $R(O, \vec{i})$ lié à un référentiel terrestre considéré galiléen. 
+&lt;b&gt;On repère la position du centre d'inertie G, à un instant $t$, par l'abscisse $x$ sur l'axe $Ox$. À l'équilibre, l'abscisse du centre d'inertie G est $x_e = 0$. On prendra $\pi^2 = 10$. La solution de l'équation différentielle s'écrit sous la forme : $x(t) = X_m \cos\left(\frac{2\pi}{T_0}t + \varphi\right)$.
+&lt;img src="/images/PHY_QCM1_5_Q2.png" alt="A" class="h-20 float-right ml-4 mb-2" /&gt;
+</t>
+  </si>
+  <si>
+    <t>&lt;b&gt; Situation 1 : &lt;/b&gt;&lt;br&gt;
+On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates (t = 0).&lt;br&gt;
+&lt;img src="/images/PHY_QCM1_5_Q3.png" alt="A" class="h-20 float-right ml-4 mb-2" /&gt;
+La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.
+&lt;div class="clear-both"&gt;&lt;/div&gt;
+&lt;br&gt;La valeur de $X_m$ vaut :</t>
+  </si>
+  <si>
     <t>&lt;b&gt;Situation 2 :&lt;/b&gt;
 &lt;br&gt; On écarte (S) de sa position d'équilibre, dans le sens positif, et on l'envoie à un instant de date $t = 0$ avec une vitesse initiale $v_0$. 
 &lt;br&gt;La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.
-&lt;br&gt;&lt;img src="/images/PHY_QCM1_5_Q3.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
-  </si>
-  <si>
-    <t>L'oscillateur mécanique étudié est constitué d'un solide (S) de centre d'inertie G et de masse $m = 200\text{ g}$ et d'un ressort à spires non jointives, de masse négligeable et de raideur $K$. Le ressort est horizontal, une de ses extrémités est fixée à un support et l'autre extrémité est accrochée au solide (S). Ce solide peut glisser sur le plan horizontal. On étudie le mouvement du centre d'inertie G dans un repère $R(O, \vec{i})$ lié à un référentiel terrestre considéré galiléen. 
-&lt;b&gt;On repère la position du centre d'inertie G, à un instant $t$, par l'abscisse $x$ sur l'axe $Ox$. À l'équilibre, l'abscisse du centre d'inertie G est $x_e = 0$. On prendra $\pi^2 = 10$. La solution de l'équation différentielle s'écrit sous la forme : $x(t) = X_m \cos\left(\frac{2\pi}{T_0}t + \varphi\right)$.
-&lt;img src="/images/PHY_QCM1_5_Q2.png" alt="A" class="h-20 float-right ml-4 mb-2" /&gt;
-&lt;b&gt; Situation 1 : &lt;/b&gt;&lt;br&gt;
-On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates (t = 0).&lt;br&gt;
-&lt;img src="/images/PHY_QCM1_5_Q3.png" alt="A" class="h-20 float-right ml-4 mb-2" /&gt;
-La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.
-&lt;div class="clear-both"&gt;&lt;/div&gt;</t>
+&lt;br&gt;&lt;img src="/images/PHY_QCM1_5_Q3.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;La valeur de $X_m$ vaut :</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Situation 3 :&lt;/b&gt; 
+On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates ($t = 0$). 
+La courbe de la figure suivante représente l'évolution au cours du temps de l'accélération $a_x$ du centre d'inertie G.
+&lt;img src="/images/PHY_QCM1_5_Q4.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;La valeur de $X_m$ vaut :</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Situation 4 :&lt;/b&gt; 
+On écarte (S) de sa position d'équilibre, dans le sens positif, et on l'envoie à un instant de date $t = 0$ avec une vitesse initiale $\vec{v}_0$ telle que $\vec{v}_0 = v_0\vec{i}$. 
+La courbe de la figure suivante représente l'évolution au cours du temps de la vitesse $v_x$ du centre d'inertie G.
+&lt;img src="/images/PHY_QCM1_5_Q5.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;La valeur de $K$ vaut :</t>
   </si>
 </sst>
 </file>
@@ -1091,7 +1096,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>3</v>
@@ -1118,7 +1123,7 @@
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
       <c r="B3" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>3</v>
@@ -1142,31 +1147,29 @@
       <c r="J3" s="9"/>
       <c r="K3" s="7"/>
     </row>
-    <row r="4" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+    <row r="4" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="10"/>
+      <c r="B4" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="14" t="s">
+      <c r="E4" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="F4" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="G4" s="14" t="s">
         <v>24</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>25</v>
       </c>
       <c r="H4" s="14"/>
       <c r="I4" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="7"/>
@@ -1174,26 +1177,26 @@
     <row r="5" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="8"/>
       <c r="B5" s="11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="F5" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="G5" s="12" t="s">
         <v>28</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>29</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J5" s="9"/>
       <c r="K5" s="7"/>
@@ -1201,84 +1204,84 @@
     <row r="6" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="13" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="F6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="G6" s="14" t="s">
         <v>32</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>33</v>
       </c>
       <c r="H6" s="14"/>
       <c r="I6" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J6" s="6"/>
       <c r="K6" s="7"/>
     </row>
     <row r="7" spans="1:11" ht="191.25" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="F7" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="G7" s="14" t="s">
         <v>36</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>37</v>
       </c>
       <c r="H7" s="14"/>
       <c r="I7" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="K7" s="7"/>
     </row>
     <row r="8" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
       <c r="B8" s="11" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="F8" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="G8" s="12" t="s">
         <v>40</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>41</v>
       </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -1286,26 +1289,26 @@
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
       <c r="B9" s="13" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="F9" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="G9" s="14" t="s">
         <v>44</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>45</v>
       </c>
       <c r="H9" s="14"/>
       <c r="I9" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
@@ -1313,55 +1316,55 @@
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="F10" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="G10" s="12" t="s">
         <v>48</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>49</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
     </row>
-    <row r="11" spans="1:11" ht="369.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="255" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>121</v>
+        <v>163</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="F11" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="G11" s="14" t="s">
         <v>52</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>53</v>
       </c>
       <c r="H11" s="14"/>
       <c r="I11" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
@@ -1369,26 +1372,26 @@
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="F12" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="G12" s="12" t="s">
         <v>56</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>57</v>
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
@@ -1396,583 +1399,577 @@
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="F13" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="G13" s="14" t="s">
         <v>60</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>61</v>
       </c>
       <c r="H13" s="14"/>
       <c r="I13" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
     </row>
     <row r="14" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="F14" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="G14" s="12" t="s">
         <v>64</v>
-      </c>
-      <c r="G14" s="12" t="s">
-        <v>65</v>
       </c>
       <c r="H14" s="12"/>
       <c r="I14" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
-        <v>165</v>
-      </c>
+      <c r="A15" s="10"/>
       <c r="B15" s="11" t="s">
-        <v>121</v>
+        <v>164</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="E15" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>74</v>
-      </c>
       <c r="G15" s="12" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10"/>
       <c r="B16" s="13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="F16" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="G16" s="14" t="s">
         <v>140</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>142</v>
       </c>
       <c r="H16" s="14"/>
       <c r="I16" s="14" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10"/>
       <c r="B17" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E17" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="G17" s="12" t="s">
         <v>143</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="G17" s="12" t="s">
-        <v>145</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
-        <v>159</v>
-      </c>
+      <c r="A18" s="10"/>
       <c r="B18" s="11" t="s">
-        <v>121</v>
+        <v>165</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E18" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="G18" s="12" t="s">
         <v>74</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>75</v>
       </c>
       <c r="H18" s="12"/>
       <c r="I18" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10"/>
       <c r="B19" s="13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="H19" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="E19" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="F19" s="14" t="s">
+      <c r="I19" s="14" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="10"/>
+      <c r="B20" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="G19" s="14" t="s">
+      <c r="E20" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="H19" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="I19" s="14" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="14" t="s">
+      <c r="F20" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="G20" s="14" t="s">
         <v>151</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>153</v>
       </c>
       <c r="H20" s="14"/>
       <c r="I20" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="11" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="F21" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="G21" s="12" t="s">
         <v>155</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="G21" s="12" t="s">
-        <v>157</v>
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="12" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10"/>
       <c r="B22" s="13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E22" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="G22" s="14" t="s">
         <v>143</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>145</v>
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="14" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="216.75" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E23" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F23" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="F23" s="12" t="s">
+      <c r="G23" s="12" t="s">
         <v>67</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>68</v>
       </c>
       <c r="H23" s="12"/>
       <c r="I23" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B24" s="13" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E24" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="F24" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="G24" s="14" t="s">
         <v>71</v>
-      </c>
-      <c r="G24" s="14" t="s">
-        <v>72</v>
       </c>
       <c r="H24" s="14"/>
       <c r="I24" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B25" s="11" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E25" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="F25" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="G25" s="12" t="s">
         <v>74</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>75</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B26" s="13" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E26" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="F26" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="G26" s="14" t="s">
         <v>78</v>
-      </c>
-      <c r="G26" s="14" t="s">
-        <v>79</v>
       </c>
       <c r="H26" s="14"/>
       <c r="I26" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="140.25" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E27" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="F27" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="G27" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="G27" s="14" t="s">
-        <v>83</v>
-      </c>
       <c r="H27" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B28" s="11" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E28" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="E28" s="12" t="s">
-        <v>85</v>
-      </c>
       <c r="F28" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B29" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="F29" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="G29" s="14" t="s">
         <v>88</v>
-      </c>
-      <c r="G29" s="14" t="s">
-        <v>89</v>
       </c>
       <c r="H29" s="14"/>
       <c r="I29" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B30" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E30" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="E30" s="12" t="s">
-        <v>91</v>
-      </c>
       <c r="F30" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="G30" s="12" t="s">
         <v>81</v>
-      </c>
-      <c r="G30" s="12" t="s">
-        <v>82</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E31" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="E31" s="12" t="s">
+      <c r="F31" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="F31" s="12" t="s">
+      <c r="G31" s="12" t="s">
         <v>94</v>
-      </c>
-      <c r="G31" s="12" t="s">
-        <v>95</v>
       </c>
       <c r="H31" s="12"/>
       <c r="I31" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="B32" s="13" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E32" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="F32" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="G32" s="14" t="s">
         <v>97</v>
-      </c>
-      <c r="G32" s="14" t="s">
-        <v>98</v>
       </c>
       <c r="H32" s="14"/>
       <c r="I32" s="14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B33" s="11" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E33" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="E33" s="12" t="s">
+      <c r="F33" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="F33" s="12" t="s">
+      <c r="G33" s="12" t="s">
         <v>101</v>
-      </c>
-      <c r="G33" s="12" t="s">
-        <v>102</v>
       </c>
       <c r="H33" s="12"/>
       <c r="I33" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B34" s="13" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E34" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="E34" s="14" t="s">
+      <c r="F34" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="F34" s="14" t="s">
+      <c r="G34" s="14" t="s">
         <v>105</v>
-      </c>
-      <c r="G34" s="14" t="s">
-        <v>106</v>
       </c>
       <c r="H34" s="14"/>
       <c r="I34" s="14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B35" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E35" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="E35" s="12" t="s">
+      <c r="F35" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="F35" s="12" t="s">
+      <c r="G35" s="12" t="s">
         <v>109</v>
-      </c>
-      <c r="G35" s="12" t="s">
-        <v>110</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/QCM5_1_PHY.xlsx
+++ b/QCM5_1_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA30024-7A86-4355-8519-1510A9D55BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E1954FF-4D89-4267-98A5-714ECF7A4195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="170">
   <si>
     <t>Question</t>
   </si>
@@ -78,18 +78,9 @@
     <t>$\frac{dx}{dt} + \frac{k}{m}x = 0$</t>
   </si>
   <si>
-    <t>$T = 20\text{ s}$</t>
-  </si>
-  <si>
     <t>$T = 2\text{ s}$</t>
   </si>
   <si>
-    <t>$T = 0,2\text{ s}$</t>
-  </si>
-  <si>
-    <t>$T = 20\text{ ms}$</t>
-  </si>
-  <si>
     <t>$F = 0,1\text{ N}$</t>
   </si>
   <si>
@@ -129,37 +120,13 @@
     <t>$4,47\text{ m.s}^{-1}$</t>
   </si>
   <si>
-    <t>$3,15\text{ m.s}^{-1}$</t>
-  </si>
-  <si>
-    <t>$2,23\text{ m.s}^{-1}$</t>
-  </si>
-  <si>
-    <t>$10\text{ m.s}^{-1}$</t>
-  </si>
-  <si>
-    <t>$-2\text{ J}$</t>
-  </si>
-  <si>
     <t>$-5\text{ J}$</t>
   </si>
   <si>
-    <t>$-10\text{ J}$</t>
-  </si>
-  <si>
-    <t>$-2,5\text{ J}$</t>
-  </si>
-  <si>
-    <t>$V_c = 2,15\text{ m.s}^{-1}$</t>
-  </si>
-  <si>
     <t>$V_c = 3,15\text{ m.s}^{-1}$</t>
   </si>
   <si>
     <t>$V_c = 5\text{ m.s}^{-1}$</t>
-  </si>
-  <si>
-    <t>$V_c = 4,47\text{ m.s}^{-1}$</t>
   </si>
   <si>
     <t>$K = 1\text{ N.m}^{-1}$</t>
@@ -524,12 +491,6 @@
   <si>
     <t>On écarte le solide de sa position d'équilibre telle que $x = 2\text{ cm}$ puis on le lâche sans vitesse initiale.
 &lt;br&gt;À l'abscisse $x = -2\text{ cm}$, la tension $F$ du ressort vaut :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L'oscillateur mécanique étudié est constitué d'un solide (S) de centre d'inertie G et de masse $m = 200\text{ g}$ et d'un ressort à spires non jointives, de masse négligeable et de raideur $K$. Le ressort est horizontal, une de ses extrémités est fixée à un support et l'autre extrémité est accrochée au solide (S). Ce solide peut glisser sur le plan horizontal. On étudie le mouvement du centre d'inertie G dans un repère $R(O, \vec{i})$ lié à un référentiel terrestre considéré galiléen. 
-&lt;b&gt;On repère la position du centre d'inertie G, à un instant $t$, par l'abscisse $x$ sur l'axe $Ox$. À l'équilibre, l'abscisse du centre d'inertie G est $x_e = 0$. On prendra $\pi^2 = 10$. La solution de l'équation différentielle s'écrit sous la forme : $x(t) = X_m \cos\left(\frac{2\pi}{T_0}t + \varphi\right)$.
-&lt;img src="/images/PHY_QCM1_5_Q2.png" alt="A" class="h-20 float-right ml-4 mb-2" /&gt;
-</t>
   </si>
   <si>
     <t>&lt;b&gt; Situation 1 : &lt;/b&gt;&lt;br&gt;
@@ -559,6 +520,55 @@
 La courbe de la figure suivante représente l'évolution au cours du temps de la vitesse $v_x$ du centre d'inertie G.
 &lt;img src="/images/PHY_QCM1_5_Q5.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
 &lt;br&gt;La valeur de $K$ vaut :</t>
+  </si>
+  <si>
+    <t>$T \approx 20\text{ s}$</t>
+  </si>
+  <si>
+    <t>$T \approx  2\text{ s}$</t>
+  </si>
+  <si>
+    <t>$T \approx  0,2\text{ s}$</t>
+  </si>
+  <si>
+    <t>$T \approx  20\text{ ms}$</t>
+  </si>
+  <si>
+    <t>$\approx 20\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$\approx 10\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$\approx 6,4\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$\approx 4,5\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$W_{BC}(f) = -10\text{ J}$</t>
+  </si>
+  <si>
+    <t>$W_{BC}(f) =-5\text{ J}$</t>
+  </si>
+  <si>
+    <t>$W_{BC}(f) =-2,5\text{ J}$</t>
+  </si>
+  <si>
+    <t>$W_{BC}(f) =5\text{ J}$</t>
+  </si>
+  <si>
+    <t>$V_c = 6,3\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$V_c = 10\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'oscillateur mécanique étudié est constitué d'un solide (S) de centre d'inertie G et de masse $m = 200\text{ g}$ et d'un ressort à spires non jointives, de masse négligeable et de raideur $K$. Le ressort est horizontal, une de ses extrémités est fixée à un support et l'autre extrémité est accrochée au solide (S). Ce solide peut glisser sur le plan horizontal. 
+&lt;img src="/images/PHY_QCM1_5_Q2.png" alt="A" class="h-20 float-right ml-4 mb-2" /&gt;
+&lt;br&gt;On étudie le mouvement du centre d'inertie G dans un repère $R(O, \vec{i})$ lié à un référentiel terrestre considéré galiléen. 
+&lt;b&gt;On repère la position du centre d'inertie G, à un instant $t$, par l'abscisse $x$ sur l'axe $Ox$. À l'équilibre, l'abscisse du centre d'inertie G est $x_e = 0$. On prendra $\pi^2 = 10$. La solution de l'équation différentielle s'écrit sous la forme : $x(t) = X_m \cos\left(\frac{2\pi}{T_0}t + \varphi\right)$.
+</t>
   </si>
 </sst>
 </file>
@@ -1096,7 +1106,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>3</v>
@@ -1123,26 +1133,26 @@
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
       <c r="B3" s="13" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>17</v>
+        <v>155</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>18</v>
+        <v>156</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>19</v>
+        <v>157</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>20</v>
+        <v>158</v>
       </c>
       <c r="H3" s="14"/>
       <c r="I3" s="14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J3" s="9"/>
       <c r="K3" s="7"/>
@@ -1150,26 +1160,26 @@
     <row r="4" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A4" s="10"/>
       <c r="B4" s="13" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="14" t="s">
         <v>21</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>24</v>
       </c>
       <c r="H4" s="14"/>
       <c r="I4" s="14" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="7"/>
@@ -1177,26 +1187,26 @@
     <row r="5" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="8"/>
       <c r="B5" s="11" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="12" t="s">
         <v>25</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>28</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="12" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J5" s="9"/>
       <c r="K5" s="7"/>
@@ -1204,84 +1214,84 @@
     <row r="6" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="13" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="14" t="s">
         <v>29</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>32</v>
       </c>
       <c r="H6" s="14"/>
       <c r="I6" s="14" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J6" s="6"/>
       <c r="K6" s="7"/>
     </row>
     <row r="7" spans="1:11" ht="191.25" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>33</v>
+        <v>159</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>34</v>
+        <v>160</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>35</v>
+        <v>161</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>36</v>
+        <v>162</v>
       </c>
       <c r="H7" s="14"/>
       <c r="I7" s="14" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="K7" s="7"/>
     </row>
     <row r="8" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
       <c r="B8" s="11" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>37</v>
+        <v>163</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>38</v>
+        <v>164</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>39</v>
+        <v>165</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>40</v>
+        <v>166</v>
       </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -1289,26 +1299,26 @@
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
       <c r="B9" s="13" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>43</v>
+        <v>167</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>44</v>
+        <v>168</v>
       </c>
       <c r="H9" s="14"/>
       <c r="I9" s="14" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
@@ -1316,55 +1326,55 @@
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="11" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
     </row>
-    <row r="11" spans="1:11" ht="255" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="280.5" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="H11" s="14"/>
       <c r="I11" s="14" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
@@ -1372,26 +1382,26 @@
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="11" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="12" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
@@ -1399,577 +1409,577 @@
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H13" s="14"/>
       <c r="I13" s="14" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
     </row>
     <row r="14" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="H14" s="12"/>
       <c r="I14" s="12" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10"/>
       <c r="B15" s="11" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="12" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10"/>
       <c r="B16" s="13" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="H16" s="14"/>
       <c r="I16" s="14" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10"/>
       <c r="B17" s="11" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17" s="12" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10"/>
       <c r="B18" s="11" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="H18" s="12"/>
       <c r="I18" s="12" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10"/>
       <c r="B19" s="13" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10"/>
       <c r="B20" s="13" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="H20" s="14"/>
       <c r="I20" s="14" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="11" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="12" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10"/>
       <c r="B22" s="13" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="14" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="216.75" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="H23" s="12"/>
       <c r="I23" s="12" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B24" s="13" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="H24" s="14"/>
       <c r="I24" s="14" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B25" s="11" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="12" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B26" s="13" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="H26" s="14"/>
       <c r="I26" s="14" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="140.25" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B28" s="11" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="12" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B29" s="13" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H29" s="14"/>
       <c r="I29" s="14" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B30" s="11" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="12" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H31" s="12"/>
       <c r="I31" s="12" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="B32" s="13" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="H32" s="14"/>
       <c r="I32" s="14" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B33" s="11" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="H33" s="12"/>
       <c r="I33" s="12" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B34" s="13" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="H34" s="14"/>
       <c r="I34" s="14" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B35" s="11" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/QCM5_1_PHY.xlsx
+++ b/QCM5_1_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E1954FF-4D89-4267-98A5-714ECF7A4195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448B4E9A-539F-4B8A-A7C7-991C3D8F3D70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="171">
   <si>
     <t>Question</t>
   </si>
@@ -460,12 +460,6 @@
   </si>
   <si>
     <t>$X_m = 6,2\text{ cm}$</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;&lt;center&gt;Le solide M&lt;/center&gt;&lt;/b&gt;
-&lt;br&gt; On considère un solide ponctuel de masse $m = 1\text{ kg}$ glissant, sans vitesse initiale, à partir du point A sur un demi-cercle vertical de rayon de $1\text{ m}$ et prolongé par une piste horizontale BC, de $2\text{ m}$ de longueur, caractérisée par une force de frottements $f = \mu \cdot R_N$ avec $\mu = 0,25$ et $R_N$ réaction normale entre le support et le solide. Le solide M continue son trajet et percute alors un ressort de raideur $k$ qu'il comprime de $10\text{ cm}$. 
-&lt;img src="/images/PHY_QCM1_5_Q1.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
-On donne $g = 10\text{ m.s}^{-2}$ ; $\sqrt{10} = 3,15$.</t>
   </si>
   <si>
     <t>&lt;br&gt;&lt;center&gt;Étude d'un système oscillant&lt;/center&gt;&lt;/br&gt; 
@@ -491,14 +485,6 @@
   <si>
     <t>On écarte le solide de sa position d'équilibre telle que $x = 2\text{ cm}$ puis on le lâche sans vitesse initiale.
 &lt;br&gt;À l'abscisse $x = -2\text{ cm}$, la tension $F$ du ressort vaut :</t>
-  </si>
-  <si>
-    <t>&lt;b&gt; Situation 1 : &lt;/b&gt;&lt;br&gt;
-On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates (t = 0).&lt;br&gt;
-&lt;img src="/images/PHY_QCM1_5_Q3.png" alt="A" class="h-20 float-right ml-4 mb-2" /&gt;
-La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.
-&lt;div class="clear-both"&gt;&lt;/div&gt;
-&lt;br&gt;La valeur de $X_m$ vaut :</t>
   </si>
   <si>
     <t>&lt;b&gt;Situation 2 :&lt;/b&gt;
@@ -564,18 +550,26 @@
     <t>$V_c = 10\text{ m.s}^{-1}$</t>
   </si>
   <si>
-    <t xml:space="preserve">L'oscillateur mécanique étudié est constitué d'un solide (S) de centre d'inertie G et de masse $m = 200\text{ g}$ et d'un ressort à spires non jointives, de masse négligeable et de raideur $K$. Le ressort est horizontal, une de ses extrémités est fixée à un support et l'autre extrémité est accrochée au solide (S). Ce solide peut glisser sur le plan horizontal. 
-&lt;img src="/images/PHY_QCM1_5_Q2.png" alt="A" class="h-20 float-right ml-4 mb-2" /&gt;
-&lt;br&gt;On étudie le mouvement du centre d'inertie G dans un repère $R(O, \vec{i})$ lié à un référentiel terrestre considéré galiléen. 
-&lt;b&gt;On repère la position du centre d'inertie G, à un instant $t$, par l'abscisse $x$ sur l'axe $Ox$. À l'équilibre, l'abscisse du centre d'inertie G est $x_e = 0$. On prendra $\pi^2 = 10$. La solution de l'équation différentielle s'écrit sous la forme : $x(t) = X_m \cos\left(\frac{2\pi}{T_0}t + \varphi\right)$.
-</t>
+    <t>&lt;b&gt;&lt;center&gt;Le solide M&lt;/center&gt;&lt;/b&gt;
+&lt;br&gt; On considère un solide ponctuel de masse $m = 1\text{ kg}$ glissant, sans vitesse initiale, à partir du point A sur un demi-cercle vertical de rayon de $1\text{ m}$ et prolongé par une piste horizontale BC, de $2\text{ m}$ de longueur, caractérisée par une force de frottements $f = \mu \cdot R_N$ avec $\mu = 0,25$ et $R_N$ réaction normale entre le support et le solide. Le solide M continue son trajet et percute alors un ressort de raideur $k$ qu'il comprime de $10\text{ cm}$. 
+On donne $g = 10\text{ m.s}^{-2}$ ; $\sqrt{10} = 3,15$.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;center&gt;&lt;b&gt;L'oscillateur mécanique&lt;/b&gt;&lt;/center&gt;
+L'oscillateur mécanique étudié est constitué d'un solide (S) de centre d'inertie G et de masse $m = 200\text{ g}$ et d'un ressort à spires non jointives, de masse négligeable et de raideur $K$. Le ressort est horizontal, une de ses extrémités est fixée à un support et l'autre extrémité est accrochée au solide (S). Ce solide peut glisser sur le plan horizontal.On étudie le mouvement du centre d'inertie G dans un repère $R(O, \vec{i})$ lié à un référentiel terrestre considéré galiléen.On repère la position du centre d'inertie G, à un instant $t$, par l'abscisse $x$ sur l'axe $Ox$. À l'équilibre, l'abscisse du centre d'inertie G est $x_e = 0$. On prendra $\pi^2 = 10$. La solution de l'équation différentielle s'écrit sous la forme : $x(t) = X_m \cos\left(\frac{2\pi}{T_0}t + \varphi\right). </t>
+  </si>
+  <si>
+    <t>PHY_QCM1_5_Q2.png</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Situation 1 :&lt;/b&gt;&lt;br&gt;On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates (t = 0).&lt;br&gt;&lt;img src="/images/PHY_QCM1_5_Q3.png" alt="Graphique" class="max-h-48 block mx-auto my-3 rounded-lg shadow-sm" /&gt;&lt;br&gt;La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.&lt;br&gt;&lt;br&gt;La valeur de $X_m$ vaut :</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -608,6 +602,11 @@
     <font>
       <sz val="10"/>
       <name val="Consolas"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="6">
@@ -708,7 +707,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -750,7 +749,10 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1139,16 +1141,16 @@
         <v>3</v>
       </c>
       <c r="D3" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="F3" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="G3" s="14" t="s">
         <v>156</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>158</v>
       </c>
       <c r="H3" s="14"/>
       <c r="I3" s="14" t="s">
@@ -1160,7 +1162,7 @@
     <row r="4" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A4" s="10"/>
       <c r="B4" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>3</v>
@@ -1238,9 +1240,9 @@
       <c r="J6" s="6"/>
       <c r="K6" s="7"/>
     </row>
-    <row r="7" spans="1:11" ht="191.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>104</v>
@@ -1249,16 +1251,16 @@
         <v>3</v>
       </c>
       <c r="D7" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="F7" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="G7" s="14" t="s">
         <v>160</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>162</v>
       </c>
       <c r="H7" s="14"/>
       <c r="I7" s="14" t="s">
@@ -1278,16 +1280,16 @@
         <v>3</v>
       </c>
       <c r="D8" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="F8" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="G8" s="12" t="s">
         <v>164</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>166</v>
       </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12" t="s">
@@ -1311,10 +1313,10 @@
         <v>33</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H9" s="14"/>
       <c r="I9" s="14" t="s">
@@ -1350,12 +1352,12 @@
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
     </row>
-    <row r="11" spans="1:11" ht="280.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="229.5" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>151</v>
+        <v>168</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>170</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>3</v>
@@ -1376,7 +1378,9 @@
       <c r="I11" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="J11" s="7"/>
+      <c r="J11" s="7" t="s">
+        <v>169</v>
+      </c>
       <c r="K11" s="7"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1460,7 +1464,7 @@
     <row r="15" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10"/>
       <c r="B15" s="11" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>3</v>
@@ -1535,7 +1539,7 @@
     <row r="18" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10"/>
       <c r="B18" s="11" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>3</v>
@@ -1587,7 +1591,7 @@
     <row r="20" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10"/>
       <c r="B20" s="13" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>3</v>
@@ -1661,7 +1665,7 @@
     </row>
     <row r="23" spans="1:9" ht="216.75" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>112</v>
@@ -1760,7 +1764,7 @@
     </row>
     <row r="27" spans="1:9" ht="140.25" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B27" s="13" t="s">
         <v>116</v>
@@ -1861,7 +1865,7 @@
     </row>
     <row r="31" spans="1:9" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>120</v>
@@ -1888,7 +1892,7 @@
     </row>
     <row r="32" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="B32" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>3</v>

--- a/QCM5_1_PHY.xlsx
+++ b/QCM5_1_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448B4E9A-539F-4B8A-A7C7-991C3D8F3D70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73E4992C-6023-4E08-A28E-58A74E2BC204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -555,14 +555,14 @@
 On donne $g = 10\text{ m.s}^{-2}$ ; $\sqrt{10} = 3,15$.</t>
   </si>
   <si>
+    <t>PHY_QCM1_5_Q2.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">&lt;center&gt;&lt;b&gt;L'oscillateur mécanique&lt;/b&gt;&lt;/center&gt;
-L'oscillateur mécanique étudié est constitué d'un solide (S) de centre d'inertie G et de masse $m = 200\text{ g}$ et d'un ressort à spires non jointives, de masse négligeable et de raideur $K$. Le ressort est horizontal, une de ses extrémités est fixée à un support et l'autre extrémité est accrochée au solide (S). Ce solide peut glisser sur le plan horizontal.On étudie le mouvement du centre d'inertie G dans un repère $R(O, \vec{i})$ lié à un référentiel terrestre considéré galiléen.On repère la position du centre d'inertie G, à un instant $t$, par l'abscisse $x$ sur l'axe $Ox$. À l'équilibre, l'abscisse du centre d'inertie G est $x_e = 0$. On prendra $\pi^2 = 10$. La solution de l'équation différentielle s'écrit sous la forme : $x(t) = X_m \cos\left(\frac{2\pi}{T_0}t + \varphi\right). </t>
-  </si>
-  <si>
-    <t>PHY_QCM1_5_Q2.png</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Situation 1 :&lt;/b&gt;&lt;br&gt;On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates (t = 0).&lt;br&gt;&lt;img src="/images/PHY_QCM1_5_Q3.png" alt="Graphique" class="max-h-48 block mx-auto my-3 rounded-lg shadow-sm" /&gt;&lt;br&gt;La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.&lt;br&gt;&lt;br&gt;La valeur de $X_m$ vaut :</t>
+L'oscillateur mécanique étudié est constitué d'un solide (S) de centre d'inertie G et de masse $m = 200\text{ g}$ et d'un ressort à spires non jointives, de masse négligeable et de raideur $K$. Le ressort est horizontal, une de ses extrémités est fixée à un support et l'autre extrémité est accrochée au solide (S). Ce solide peut glisser sur le plan horizontal.On étudie le mouvement du centre d'inertie G dans un repère $R(O, \vec{i})$ lié à un référentiel terrestre considéré galiléen.On repère la position du centre d'inertie G, à un instant $t$, par l'abscisse $x$ sur l'axe $Ox$. À l'équilibre, l'abscisse du centre d'inertie G est $x_0$. On prendra $\pi^2 = 10$. La solution de l'équation différentielle s'écrit sous la forme : $x(t) = X_m \cos\left(\frac{2\pi}{T_0}t + \varphi\right)$. </t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Situation 1 :&lt;/b&gt;&lt;br&gt;On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates (t = 0).&lt;br&gt;&lt;img src='/images/PHY_QCM1_5_Q3.png' alt='Graphique' class='max-h-48 block mx-auto my-3 rounded-lg shadow-sm' /&gt;&lt;br&gt;La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.&lt;br&gt;&lt;br&gt;La valeur de $X_m$ vaut :</t>
   </si>
 </sst>
 </file>
@@ -1354,7 +1354,7 @@
     </row>
     <row r="11" spans="1:11" ht="229.5" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>170</v>
@@ -1379,7 +1379,7 @@
         <v>39</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K11" s="7"/>
     </row>

--- a/QCM5_1_PHY.xlsx
+++ b/QCM5_1_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73E4992C-6023-4E08-A28E-58A74E2BC204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{490769B8-19FC-4FA3-9523-C58C2A4102FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -562,7 +562,7 @@
 L'oscillateur mécanique étudié est constitué d'un solide (S) de centre d'inertie G et de masse $m = 200\text{ g}$ et d'un ressort à spires non jointives, de masse négligeable et de raideur $K$. Le ressort est horizontal, une de ses extrémités est fixée à un support et l'autre extrémité est accrochée au solide (S). Ce solide peut glisser sur le plan horizontal.On étudie le mouvement du centre d'inertie G dans un repère $R(O, \vec{i})$ lié à un référentiel terrestre considéré galiléen.On repère la position du centre d'inertie G, à un instant $t$, par l'abscisse $x$ sur l'axe $Ox$. À l'équilibre, l'abscisse du centre d'inertie G est $x_0$. On prendra $\pi^2 = 10$. La solution de l'équation différentielle s'écrit sous la forme : $x(t) = X_m \cos\left(\frac{2\pi}{T_0}t + \varphi\right)$. </t>
   </si>
   <si>
-    <t>&lt;b&gt;Situation 1 :&lt;/b&gt;&lt;br&gt;On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates (t = 0).&lt;br&gt;&lt;img src='/images/PHY_QCM1_5_Q3.png' alt='Graphique' class='max-h-48 block mx-auto my-3 rounded-lg shadow-sm' /&gt;&lt;br&gt;La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.&lt;br&gt;&lt;br&gt;La valeur de $X_m$ vaut :</t>
+    <t>&lt;b&gt;Situation 1 :&lt;/b&gt;&lt;br /&gt;On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates (t = 0).&lt;br /&gt;&lt;img src="/images/PHY_QCM1_5_Q3.png" alt="Graphique" className="max-h-48 block mx-auto my-3 rounded-lg shadow-sm" /&gt;&lt;br /&gt;La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.&lt;br /&gt;&lt;br /&gt;La valeur de $X_m$ vaut :</t>
   </si>
 </sst>
 </file>

--- a/QCM5_1_PHY.xlsx
+++ b/QCM5_1_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{490769B8-19FC-4FA3-9523-C58C2A4102FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE312A01-F5E6-49CD-A90B-72513D0269E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -562,7 +562,7 @@
 L'oscillateur mécanique étudié est constitué d'un solide (S) de centre d'inertie G et de masse $m = 200\text{ g}$ et d'un ressort à spires non jointives, de masse négligeable et de raideur $K$. Le ressort est horizontal, une de ses extrémités est fixée à un support et l'autre extrémité est accrochée au solide (S). Ce solide peut glisser sur le plan horizontal.On étudie le mouvement du centre d'inertie G dans un repère $R(O, \vec{i})$ lié à un référentiel terrestre considéré galiléen.On repère la position du centre d'inertie G, à un instant $t$, par l'abscisse $x$ sur l'axe $Ox$. À l'équilibre, l'abscisse du centre d'inertie G est $x_0$. On prendra $\pi^2 = 10$. La solution de l'équation différentielle s'écrit sous la forme : $x(t) = X_m \cos\left(\frac{2\pi}{T_0}t + \varphi\right)$. </t>
   </si>
   <si>
-    <t>&lt;b&gt;Situation 1 :&lt;/b&gt;&lt;br /&gt;On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates (t = 0).&lt;br /&gt;&lt;img src="/images/PHY_QCM1_5_Q3.png" alt="Graphique" className="max-h-48 block mx-auto my-3 rounded-lg shadow-sm" /&gt;&lt;br /&gt;La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.&lt;br /&gt;&lt;br /&gt;La valeur de $X_m$ vaut :</t>
+    <t>&lt;b&gt;Situation 1 :&lt;/b&gt;&lt;br /&gt;On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates (t = 0).&lt;br /&gt;La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.&lt;br /&gt;&lt;br /&gt;La valeur de $X_m$ vaut :</t>
   </si>
 </sst>
 </file>

--- a/QCM5_1_PHY.xlsx
+++ b/QCM5_1_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE312A01-F5E6-49CD-A90B-72513D0269E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B8C616-551E-4E25-85EB-641503E1A77A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -562,14 +562,14 @@
 L'oscillateur mécanique étudié est constitué d'un solide (S) de centre d'inertie G et de masse $m = 200\text{ g}$ et d'un ressort à spires non jointives, de masse négligeable et de raideur $K$. Le ressort est horizontal, une de ses extrémités est fixée à un support et l'autre extrémité est accrochée au solide (S). Ce solide peut glisser sur le plan horizontal.On étudie le mouvement du centre d'inertie G dans un repère $R(O, \vec{i})$ lié à un référentiel terrestre considéré galiléen.On repère la position du centre d'inertie G, à un instant $t$, par l'abscisse $x$ sur l'axe $Ox$. À l'équilibre, l'abscisse du centre d'inertie G est $x_0$. On prendra $\pi^2 = 10$. La solution de l'équation différentielle s'écrit sous la forme : $x(t) = X_m \cos\left(\frac{2\pi}{T_0}t + \varphi\right)$. </t>
   </si>
   <si>
-    <t>&lt;b&gt;Situation 1 :&lt;/b&gt;&lt;br /&gt;On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates (t = 0).&lt;br /&gt;La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.&lt;br /&gt;&lt;br /&gt;La valeur de $X_m$ vaut :</t>
+    <t>&lt;b&gt;Situation 1 :&lt;/b&gt;&lt;br /&gt;On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates (t = 0).&lt;br /&gt;&lt;img src="/images/PHY_QCM1_5_Q3.png" alt="Graphique" className="max-h-48 block mx-auto my-3 rounded-lg shadow-sm" /&gt;&lt;br /&gt;La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.&lt;br /&gt;&lt;br /&gt;La valeur de $X_m$ vaut :</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -598,10 +598,7 @@
       <b/>
       <sz val="10"/>
       <name val="Consolas"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Consolas"/>
+      <family val="3"/>
     </font>
     <font>
       <sz val="10"/>
@@ -707,7 +704,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -750,9 +747,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1356,7 +1350,7 @@
       <c r="A11" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="13" t="s">
         <v>170</v>
       </c>
       <c r="C11" s="5" t="s">

--- a/QCM5_1_PHY.xlsx
+++ b/QCM5_1_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B8C616-551E-4E25-85EB-641503E1A77A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E991B96D-FEDC-4AF1-A671-AB0261A72890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -562,7 +562,7 @@
 L'oscillateur mécanique étudié est constitué d'un solide (S) de centre d'inertie G et de masse $m = 200\text{ g}$ et d'un ressort à spires non jointives, de masse négligeable et de raideur $K$. Le ressort est horizontal, une de ses extrémités est fixée à un support et l'autre extrémité est accrochée au solide (S). Ce solide peut glisser sur le plan horizontal.On étudie le mouvement du centre d'inertie G dans un repère $R(O, \vec{i})$ lié à un référentiel terrestre considéré galiléen.On repère la position du centre d'inertie G, à un instant $t$, par l'abscisse $x$ sur l'axe $Ox$. À l'équilibre, l'abscisse du centre d'inertie G est $x_0$. On prendra $\pi^2 = 10$. La solution de l'équation différentielle s'écrit sous la forme : $x(t) = X_m \cos\left(\frac{2\pi}{T_0}t + \varphi\right)$. </t>
   </si>
   <si>
-    <t>&lt;b&gt;Situation 1 :&lt;/b&gt;&lt;br /&gt;On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates (t = 0).&lt;br /&gt;&lt;img src="/images/PHY_QCM1_5_Q3.png" alt="Graphique" className="max-h-48 block mx-auto my-3 rounded-lg shadow-sm" /&gt;&lt;br /&gt;La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.&lt;br /&gt;&lt;br /&gt;La valeur de $X_m$ vaut :</t>
+    <t>&lt;b&gt;Situation 1 :&lt;/b&gt;&lt;br&gt;On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates (t = 0).&lt;br&gt;[[IMG=PHY_QCM1_5_Q3.png]]&lt;br&gt;La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.&lt;br&gt;&lt;br&gt;La valeur de $X_m$ vaut :</t>
   </si>
 </sst>
 </file>

--- a/QCM5_1_PHY.xlsx
+++ b/QCM5_1_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E991B96D-FEDC-4AF1-A671-AB0261A72890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA55CB7-619E-4805-8031-A43C5CB24BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="174">
   <si>
     <t>Question</t>
   </si>
@@ -198,9 +198,6 @@
     <t>$K = 80\text{ N.m}^{-1}$</t>
   </si>
   <si>
-    <t>$E_m = 4\text{ mJ}$</t>
-  </si>
-  <si>
     <t>$E_m = 8\text{ mJ}$</t>
   </si>
   <si>
@@ -219,18 +216,9 @@
     <t>$X_m = 8\text{ cm}$</t>
   </si>
   <si>
-    <t>$x_1 = 0,865\text{ cm}$</t>
-  </si>
-  <si>
-    <t>$x_1 = 1,73\text{ cm}$</t>
-  </si>
-  <si>
     <t>$x_1 = -3,46\text{ cm}$</t>
   </si>
   <si>
-    <t>$x_1 = 5,19\text{ cm}$</t>
-  </si>
-  <si>
     <t>$0,04\text{ mJ}$</t>
   </si>
   <si>
@@ -240,9 +228,6 @@
     <t>$4 \cdot 10^{-5}\text{ J}$</t>
   </si>
   <si>
-    <t>$4 \cdot 10^{-4}\text{ J}$</t>
-  </si>
-  <si>
     <t>$0,02\text{ mJ}$</t>
   </si>
   <si>
@@ -255,9 +240,6 @@
     <t>$\omega_0 = 2\text{ rad.s}^{-1}$</t>
   </si>
   <si>
-    <t>$\omega_0 = 4\text{ rad.s}^{-1}$</t>
-  </si>
-  <si>
     <t>$\omega_0 = 10\text{ rad.s}^{-1}$</t>
   </si>
   <si>
@@ -285,9 +267,6 @@
     <t>$\omega_0 = 5\text{ rad.s}^{-1}$</t>
   </si>
   <si>
-    <t>$\omega_0 = 20\text{ rad.s}^{-1}$</t>
-  </si>
-  <si>
     <t>$x(t) = 2,8 \cdot 10^{-2} \cos(10t - \frac{\pi}{4})$</t>
   </si>
   <si>
@@ -306,21 +285,12 @@
     <t>$t_1 = \frac{\pi}{40}\text{ s}$</t>
   </si>
   <si>
-    <t>$t_1 = \frac{3\pi}{40}\text{ s}$</t>
-  </si>
-  <si>
-    <t>$t_1 = \frac{\pi}{10}\text{ s}$</t>
-  </si>
-  <si>
     <t>$t_2 = \frac{3\pi}{20}\text{ s}$</t>
   </si>
   <si>
     <t>$t_2 = \frac{3\pi}{40}\text{ s}$</t>
   </si>
   <si>
-    <t>$t_2 = \frac{\pi}{40}\text{ s}$</t>
-  </si>
-  <si>
     <t>$t_2 = \frac{3\pi}{2}\text{ s}$</t>
   </si>
   <si>
@@ -366,9 +336,6 @@
     <t>La valeur de $K$ vaut :</t>
   </si>
   <si>
-    <t>L'énergie mécanique $E_m$ est :</t>
-  </si>
-  <si>
     <t>L'amplitude $X_m$ vaut :</t>
   </si>
   <si>
@@ -420,9 +387,6 @@
     <t>$\varphi = -\frac{\pi}{3}$</t>
   </si>
   <si>
-    <t>$\varphi = -\frac{\pi}{4}$</t>
-  </si>
-  <si>
     <t>$\varphi = -\frac{\pi}{6}$</t>
   </si>
   <si>
@@ -460,109 +424,164 @@
   </si>
   <si>
     <t>$X_m = 6,2\text{ cm}$</t>
-  </si>
-  <si>
-    <t>&lt;br&gt;&lt;center&gt;Étude d'un système oscillant&lt;/center&gt;&lt;/br&gt; 
-Le solide (S) de masse $m = 200\text{ g}$ est fixé à un ressort horizontal à spires non jointives, de masse négligeable et de raideur $K$. A l'équilibre, le centre d'inertie G coïncide avec l'origine du repère $(O, \vec{i})$ lié à un référentiel terrestre considéré galiléen (Figure 2). 
-&lt;img src="/images/PHY_QCM1_6_Q2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
-On écarte (S) dans le sens positif d'une distance $X_m$ et on l'abandonne sans vitesse initiale à $t_0 = 0$. Le solide effectue $20$ oscillations pendant $\Delta t = 12,6\text{ s}$. On donne : $(12,6)^2 \approx 160 ; \pi^2 = 10 ; \sqrt{3} \approx 1,73$.</t>
-  </si>
-  <si>
-    <t>&lt;br&gt;&lt;center&gt;Un pendule élastique &lt;/center&gt;&lt;/br&gt;
-Une masse $m = 25\text{ g}$ est attachée à l'extrémité d'un ressort horizontal, de constante de raideur $k = 0,2\text{ N.m}^{-1}$ et de longueur à vide $L_0 = 10\text{ cm}$. L'autre extrémité est fixée à un point fixe O. A est le point d'abscisse $OA = 12\text{ cm}$ et B est le point d'abscisse $OB = 8\text{ cm}$. On lâche $m$ de A avec une vitesse nulle.
-&lt;img src="/images/PHY_QCM1_7_Q2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;br&gt;&lt;center&gt;Une tige horizontale &lt;/center&gt;&lt;/br&gt;
- Soit le pendule élastique constitué d'un cylindre de masse $m = 200\text{ g}$ attachée à un ressort dont la constante de raideur est $k = 20\text{ N.m}^{-1}$. On donne : $2\pi \approx 6,3 ; \sqrt{10} = 3,2 ; 6,3 \times 3,2 = 20$. On considère que l'ensemble peut coulisser sans frottements sur une tige horizontale. Lorsque le cylindre est en équilibre, son centre d'inertie coïncide avec la graduation O de l'axe.
-&lt;img src="/images/PHY_QCM1_8_Q2.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> On écarte le solide de sa position d'équilibre d'une distance $x = 2,0\text{ cm}$ puis on le lance avec une vitesse $v_{0x} = 0,20\text{ m.s}^{-1}$.
-&lt;b&gt;La pulsation du mouvement vaut :</t>
   </si>
   <si>
     <t>On écarte le solide de sa position d'équilibre telle que $x = 2\text{ cm}$ puis on le lâche sans vitesse initiale.
 &lt;br&gt;À l'abscisse $x = -2\text{ cm}$, la tension $F$ du ressort vaut :</t>
+  </si>
+  <si>
+    <t>$T \approx 20\text{ s}$</t>
+  </si>
+  <si>
+    <t>$T \approx  2\text{ s}$</t>
+  </si>
+  <si>
+    <t>$T \approx  0,2\text{ s}$</t>
+  </si>
+  <si>
+    <t>$T \approx  20\text{ ms}$</t>
+  </si>
+  <si>
+    <t>$\approx 20\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$\approx 10\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$\approx 6,4\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$\approx 4,5\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$W_{BC}(f) = -10\text{ J}$</t>
+  </si>
+  <si>
+    <t>$W_{BC}(f) =-5\text{ J}$</t>
+  </si>
+  <si>
+    <t>$W_{BC}(f) =-2,5\text{ J}$</t>
+  </si>
+  <si>
+    <t>$W_{BC}(f) =5\text{ J}$</t>
+  </si>
+  <si>
+    <t>$V_c = 6,3\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$V_c = 10\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;&lt;center&gt;Le solide M&lt;/center&gt;&lt;/b&gt;
+&lt;br&gt; On considère un solide ponctuel de masse $m = 1\text{ kg}$ glissant, sans vitesse initiale, à partir du point A sur un demi-cercle vertical de rayon de $1\text{ m}$ et prolongé par une piste horizontale BC, de $2\text{ m}$ de longueur, caractérisée par une force de frottements $f = \mu \cdot R_N$ avec $\mu = 0,25$ et $R_N$ réaction normale entre le support et le solide. Le solide M continue son trajet et percute alors un ressort de raideur $k$ qu'il comprime de $10\text{ cm}$. 
+On donne $g = 10\text{ m.s}^{-2}$ ; $\sqrt{10} = 3,15$.</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_5_Q2.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;center&gt;&lt;b&gt;L'oscillateur mécanique&lt;/b&gt;&lt;/center&gt;
+L'oscillateur mécanique étudié est constitué d'un solide (S) de centre d'inertie G et de masse $m = 200\text{ g}$ et d'un ressort à spires non jointives, de masse négligeable et de raideur $K$. Le ressort est horizontal, une de ses extrémités est fixée à un support et l'autre extrémité est accrochée au solide (S). Ce solide peut glisser sur le plan horizontal.On étudie le mouvement du centre d'inertie G dans un repère $R(O, \vec{i})$ lié à un référentiel terrestre considéré galiléen.On repère la position du centre d'inertie G, à un instant $t$, par l'abscisse $x$ sur l'axe $Ox$. À l'équilibre, l'abscisse du centre d'inertie G est $x_0$. On prendra $\pi^2 = 10$. La solution de l'équation différentielle s'écrit sous la forme : $x(t) = X_m \cos\left(\frac{2\pi}{T_0}t + \varphi\right)$. </t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Situation 1 :&lt;/b&gt;&lt;br&gt;On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates (t = 0).&lt;br&gt;[[IMG=PHY_QCM1_5_Q3.png]]&lt;br&gt;La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.&lt;br&gt;&lt;br&gt;La valeur de $X_m$ vaut :</t>
   </si>
   <si>
     <t>&lt;b&gt;Situation 2 :&lt;/b&gt;
 &lt;br&gt; On écarte (S) de sa position d'équilibre, dans le sens positif, et on l'envoie à un instant de date $t = 0$ avec une vitesse initiale $v_0$. 
 &lt;br&gt;La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.
-&lt;br&gt;&lt;img src="/images/PHY_QCM1_5_Q3.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;br&gt;&lt;img src="/images/PHY_QCM1_5_Q4.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
 &lt;br&gt;La valeur de $X_m$ vaut :</t>
   </si>
   <si>
     <t>&lt;b&gt;Situation 3 :&lt;/b&gt; 
 On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates ($t = 0$). 
 La courbe de la figure suivante représente l'évolution au cours du temps de l'accélération $a_x$ du centre d'inertie G.
-&lt;img src="/images/PHY_QCM1_5_Q4.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;img src="/images/PHY_QCM1_5_Q5.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
 &lt;br&gt;La valeur de $X_m$ vaut :</t>
   </si>
   <si>
     <t>&lt;b&gt;Situation 4 :&lt;/b&gt; 
 On écarte (S) de sa position d'équilibre, dans le sens positif, et on l'envoie à un instant de date $t = 0$ avec une vitesse initiale $\vec{v}_0$ telle que $\vec{v}_0 = v_0\vec{i}$. 
 La courbe de la figure suivante représente l'évolution au cours du temps de la vitesse $v_x$ du centre d'inertie G.
-&lt;img src="/images/PHY_QCM1_5_Q5.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+&lt;img src="/images/PHY_QCM1_5_Q6.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
 &lt;br&gt;La valeur de $K$ vaut :</t>
   </si>
   <si>
-    <t>$T \approx 20\text{ s}$</t>
-  </si>
-  <si>
-    <t>$T \approx  2\text{ s}$</t>
-  </si>
-  <si>
-    <t>$T \approx  0,2\text{ s}$</t>
-  </si>
-  <si>
-    <t>$T \approx  20\text{ ms}$</t>
-  </si>
-  <si>
-    <t>$\approx 20\text{ m.s}^{-1}$</t>
-  </si>
-  <si>
-    <t>$\approx 10\text{ m.s}^{-1}$</t>
-  </si>
-  <si>
-    <t>$\approx 6,4\text{ m.s}^{-1}$</t>
-  </si>
-  <si>
-    <t>$\approx 4,5\text{ m.s}^{-1}$</t>
-  </si>
-  <si>
-    <t>$W_{BC}(f) = -10\text{ J}$</t>
-  </si>
-  <si>
-    <t>$W_{BC}(f) =-5\text{ J}$</t>
-  </si>
-  <si>
-    <t>$W_{BC}(f) =-2,5\text{ J}$</t>
-  </si>
-  <si>
-    <t>$W_{BC}(f) =5\text{ J}$</t>
-  </si>
-  <si>
-    <t>$V_c = 6,3\text{ m.s}^{-1}$</t>
-  </si>
-  <si>
-    <t>$V_c = 10\text{ m.s}^{-1}$</t>
-  </si>
-  <si>
-    <t>&lt;b&gt;&lt;center&gt;Le solide M&lt;/center&gt;&lt;/b&gt;
-&lt;br&gt; On considère un solide ponctuel de masse $m = 1\text{ kg}$ glissant, sans vitesse initiale, à partir du point A sur un demi-cercle vertical de rayon de $1\text{ m}$ et prolongé par une piste horizontale BC, de $2\text{ m}$ de longueur, caractérisée par une force de frottements $f = \mu \cdot R_N$ avec $\mu = 0,25$ et $R_N$ réaction normale entre le support et le solide. Le solide M continue son trajet et percute alors un ressort de raideur $k$ qu'il comprime de $10\text{ cm}$. 
-On donne $g = 10\text{ m.s}^{-2}$ ; $\sqrt{10} = 3,15$.</t>
-  </si>
-  <si>
-    <t>PHY_QCM1_5_Q2.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;center&gt;&lt;b&gt;L'oscillateur mécanique&lt;/b&gt;&lt;/center&gt;
-L'oscillateur mécanique étudié est constitué d'un solide (S) de centre d'inertie G et de masse $m = 200\text{ g}$ et d'un ressort à spires non jointives, de masse négligeable et de raideur $K$. Le ressort est horizontal, une de ses extrémités est fixée à un support et l'autre extrémité est accrochée au solide (S). Ce solide peut glisser sur le plan horizontal.On étudie le mouvement du centre d'inertie G dans un repère $R(O, \vec{i})$ lié à un référentiel terrestre considéré galiléen.On repère la position du centre d'inertie G, à un instant $t$, par l'abscisse $x$ sur l'axe $Ox$. À l'équilibre, l'abscisse du centre d'inertie G est $x_0$. On prendra $\pi^2 = 10$. La solution de l'équation différentielle s'écrit sous la forme : $x(t) = X_m \cos\left(\frac{2\pi}{T_0}t + \varphi\right)$. </t>
-  </si>
-  <si>
-    <t>&lt;b&gt;Situation 1 :&lt;/b&gt;&lt;br&gt;On écarte (S) de sa position d'équilibre et on le lâche sans vitesse initiale à un instant choisi comme origine des dates (t = 0).&lt;br&gt;[[IMG=PHY_QCM1_5_Q3.png]]&lt;br&gt;La courbe de la figure suivante représente l'évolution au cours du temps de l'abscisse $x$ du centre d'inertie G.&lt;br&gt;&lt;br&gt;La valeur de $X_m$ vaut :</t>
+    <t>&lt;br&gt;&lt;center&gt;Étude d'un système oscillant&lt;/center&gt;&lt;/br&gt; 
+Le solide (S) de masse $m = 200\text{ g}$ est fixé à un ressort horizontal à spires non jointives, de masse négligeable et de raideur $K$. A l'équilibre, le centre d'inertie G de (S) coïncide avec l'origine du repère $(O, \vec{i})$ lié à un référentiel terrestre considéré galiléen (Figure 2). Tous les frottements sont négligeables. 
+&lt;img src="/images/PHY_QCM1_5_Q7.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+On écarte (S) de sa position d'équilibre dans le sens positif d'une distance $X_m$ et on l'abandonne sans vitesse initiale à $t_0 = 0$. Le solide ( S) effectue alors un mouvement de
+translation rectiligne sinusoïdal de période $T_0$. 
+Le solide (S) effectue $20$ oscillations pendant $\Delta t = 12,6\text{ s}$. 
+On donne : $(12,6)^2 \approx 160 ; \pi^2 \approx 10 ; \sqrt{3} \approx 1,73$.</t>
+  </si>
+  <si>
+    <t>On choisit l'état de référence de l'énergie potentielle élastique Epe et le plan horizontal contenant G comme état de référence de l'énergie
+potentielle de pesanteur $E_{PP}$ .
+La courbe de la figure 3 représente le diagramme d'énergie cinétique
+E_c = f (t) du solide. 
+&lt;br&gt;L'énergie mécanique $E_m$ est :</t>
+  </si>
+  <si>
+    <t>PHY_QCM1_5_Q8.png</t>
+  </si>
+  <si>
+    <t>$E_m = 0\text{ mJ}$</t>
+  </si>
+  <si>
+    <t>$x_1 \approx 0,865\text{ cm}$</t>
+  </si>
+  <si>
+    <t>$x_1 \approx 1,73\text{ cm}$</t>
+  </si>
+  <si>
+    <t>$x_1 \approx 3,46\text{ cm}$</t>
+  </si>
+  <si>
+    <t>$x_1 \approx 5,19\text{ cm}$</t>
+  </si>
+  <si>
+    <t>$\omega_0 = \sqrt{8}\text{ rad.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$\omega_0 = 8\text{ rad.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$\omega_0 = \sqrt{2}\text{ rad.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>L'énergie cinétique de m en A vaut :</t>
+  </si>
+  <si>
+    <t>&lt;br&gt;&lt;center&gt;Un pendule élastique &lt;/center&gt;&lt;/br&gt;
+Une masse $m = 25\text{ g}$ est attachée à l'extrémité d'un ressort horizontal, de constante de raideur $k = 0,2\text{ N.m}^{-1}$ et de longueur à vide $L_0 = 10\text{ cm}$. L'autre extrémité du ressort est fixée à un point fixe O. 
+A est le point d'abscisse $OA = 12\text{ cm}$ et B est le point d'abscisse $OB = 8\text{ cm}$. On lâche $m$ de A avec une vitesse nulle. Cette masse se déplace sans frottement sur le plan horizontal selon l'axe Ox.
+&lt;img src="/images/PHY_QCM1_5_Q9.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;br&gt;&lt;center&gt;Une tige horizontale &lt;/center&gt;&lt;/br&gt;
+ Soit le pendule élastique ci-dessous constitué d'un cylindre de masse $m = 200\text{ g}$ attachée à un ressort dont la constante de raideur est $k = 20\text{ N.m}^{-1}$. 
+On donne : $2\pi \approx 6,3 ; $\quad$ \sqrt{10} \approx 3,2 ; $\quad$ 6,3 \times 3,2 \approx 20$. 
+On considère que l'ensemble peut coulisser sans frottements sur une tige horizontale. Lorsque le cylindre est en équilibre, son centre d'inertie coïncide avec la graduation O de l'axe.
+&lt;img src="/images/PHY_QCM1_5_Q10.png" alt="A"class="h-20 block ml-auto my-1" /&gt;
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> On écarte le solide de sa position d'équilibre d'une distance $x = 2,0\text{ cm}$ puis on le lance avec une vitesse de composante $v_{0x} = 0,20\text{ m.s}^{-1}$.
+&lt;br&gt;La pulsation du mouvement vaut :</t>
+  </si>
+  <si>
+    <t>$\omega_0 = 2,5\text{ rad.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$t_1 = \frac{\pi}{4}\text{ s}$</t>
+  </si>
+  <si>
+    <t>$t_1 = \frac{\pi}{2}\text{ s}$</t>
+  </si>
+  <si>
+    <t>$t_2 = \frac{3\pi}{4}\text{ s}$</t>
   </si>
 </sst>
 </file>
@@ -704,7 +723,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -747,6 +766,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1051,7 +1073,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52.28515625" customWidth="1"/>
@@ -1102,7 +1124,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>3</v>
@@ -1129,22 +1151,22 @@
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
       <c r="B3" s="13" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="H3" s="14"/>
       <c r="I3" s="14" t="s">
@@ -1156,7 +1178,7 @@
     <row r="4" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A4" s="10"/>
       <c r="B4" s="13" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>3</v>
@@ -1183,7 +1205,7 @@
     <row r="5" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="8"/>
       <c r="B5" s="11" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>3</v>
@@ -1210,7 +1232,7 @@
     <row r="6" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="13" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>3</v>
@@ -1236,54 +1258,54 @@
     </row>
     <row r="7" spans="1:11" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="H7" s="14"/>
       <c r="I7" s="14" t="s">
         <v>30</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="K7" s="7"/>
     </row>
     <row r="8" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
       <c r="B8" s="11" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12" t="s">
@@ -1295,7 +1317,7 @@
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
       <c r="B9" s="13" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>3</v>
@@ -1307,10 +1329,10 @@
         <v>33</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="H9" s="14"/>
       <c r="I9" s="14" t="s">
@@ -1322,7 +1344,7 @@
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="11" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>3</v>
@@ -1348,10 +1370,10 @@
     </row>
     <row r="11" spans="1:11" ht="229.5" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>3</v>
@@ -1373,14 +1395,14 @@
         <v>39</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="K11" s="7"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="11" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>3</v>
@@ -1407,22 +1429,22 @@
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="14" t="s">
-        <v>47</v>
-      </c>
       <c r="F13" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" s="14" t="s">
         <v>48</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>49</v>
       </c>
       <c r="H13" s="14"/>
       <c r="I13" s="14" t="s">
@@ -1433,22 +1455,22 @@
     </row>
     <row r="14" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="F14" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="G14" s="12" t="s">
         <v>52</v>
-      </c>
-      <c r="G14" s="12" t="s">
-        <v>53</v>
       </c>
       <c r="H14" s="12"/>
       <c r="I14" s="12" t="s">
@@ -1458,107 +1480,107 @@
     <row r="15" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10"/>
       <c r="B15" s="11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E15" s="12" t="s">
         <v>39</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10"/>
       <c r="B16" s="13" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="H16" s="14"/>
       <c r="I16" s="14" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10"/>
       <c r="B17" s="11" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17" s="12" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10"/>
       <c r="B18" s="11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="E18" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="G18" s="12" t="s">
         <v>62</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>63</v>
       </c>
       <c r="H18" s="12"/>
       <c r="I18" s="12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10"/>
       <c r="B19" s="13" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>3</v>
@@ -1567,13 +1589,13 @@
         <v>46</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="H19" s="14" t="s">
         <v>47</v>
@@ -1582,87 +1604,87 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10"/>
       <c r="B20" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="H20" s="14"/>
       <c r="I20" s="14" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="11" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="12" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10"/>
       <c r="B22" s="13" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="14" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="216.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
-        <v>145</v>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="267.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="16" t="s">
+        <v>155</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>3</v>
@@ -1684,300 +1706,327 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="102" x14ac:dyDescent="0.25">
       <c r="B24" s="13" t="s">
-        <v>113</v>
+        <v>156</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="E24" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="F24" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="G24" s="14" t="s">
         <v>59</v>
-      </c>
-      <c r="G24" s="14" t="s">
-        <v>60</v>
       </c>
       <c r="H24" s="14"/>
       <c r="I24" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B25" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" s="12" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B25" s="11" t="s">
+      <c r="F25" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G25" s="12" t="s">
         <v>114</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>63</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B26" s="13" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>64</v>
+        <v>159</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>67</v>
+        <v>162</v>
       </c>
       <c r="H26" s="14"/>
       <c r="I26" s="14" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="140.25" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
-        <v>146</v>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="165.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="16" t="s">
+        <v>167</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E27" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="E27" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="F27" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="G27" s="14" t="s">
-        <v>71</v>
+      <c r="F27" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>64</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B28" s="11" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="12" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B29" s="13" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>75</v>
+        <v>163</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>76</v>
+        <v>165</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H29" s="14"/>
       <c r="I29" s="14" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B30" s="11" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="165.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
-        <v>147</v>
-      </c>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B31" s="11" t="s">
-        <v>120</v>
+        <v>166</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H31" s="12"/>
       <c r="I31" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="178.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="G32" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="B33" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B34" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="E34" s="12" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="B32" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="E32" s="14" t="s">
+      <c r="F34" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B35" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="F35" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="G35" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="G32" s="14" t="s">
+      <c r="H35" s="14"/>
+      <c r="I35" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B36" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B33" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="12" t="s">
+      <c r="E36" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="F36" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="E33" s="12" t="s">
+      <c r="G36" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="F33" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="G33" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12" t="s">
+      <c r="H36" s="12"/>
+      <c r="I36" s="12" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B34" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="F34" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="G34" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="H34" s="14"/>
-      <c r="I34" s="14" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="35" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B35" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="E35" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="F35" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="G35" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/QCM5_1_PHY.xlsx
+++ b/QCM5_1_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA55CB7-619E-4805-8031-A43C5CB24BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{475F6FDF-D35A-4E04-B7AB-0B41DD8407F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="170">
   <si>
     <t>Question</t>
   </si>
@@ -117,9 +117,6 @@
     <t>$E_p = 2,5 \cdot 10^{-4}\text{ J}$</t>
   </si>
   <si>
-    <t>$4,47\text{ m.s}^{-1}$</t>
-  </si>
-  <si>
     <t>$-5\text{ J}$</t>
   </si>
   <si>
@@ -216,9 +213,6 @@
     <t>$X_m = 8\text{ cm}$</t>
   </si>
   <si>
-    <t>$x_1 = -3,46\text{ cm}$</t>
-  </si>
-  <si>
     <t>$0,04\text{ mJ}$</t>
   </si>
   <si>
@@ -234,9 +228,6 @@
     <t>$0,2\text{ mJ}$</t>
   </si>
   <si>
-    <t>$\omega_0 = 2\sqrt{2}\text{ rad.s}^{-1}$</t>
-  </si>
-  <si>
     <t>$\omega_0 = 2\text{ rad.s}^{-1}$</t>
   </si>
   <si>
@@ -292,9 +283,6 @@
   </si>
   <si>
     <t>$t_2 = \frac{3\pi}{2}\text{ s}$</t>
-  </si>
-  <si>
-    <t>Option A et C</t>
   </si>
   <si>
     <t>L'équation différentielle du mouvement s'écrit :</t>
@@ -1124,7 +1112,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>3</v>
@@ -1151,22 +1139,22 @@
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
       <c r="B3" s="13" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="H3" s="14"/>
       <c r="I3" s="14" t="s">
@@ -1178,7 +1166,7 @@
     <row r="4" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A4" s="10"/>
       <c r="B4" s="13" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>3</v>
@@ -1205,7 +1193,7 @@
     <row r="5" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="8"/>
       <c r="B5" s="11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>3</v>
@@ -1232,7 +1220,7 @@
     <row r="6" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="13" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>3</v>
@@ -1258,58 +1246,58 @@
     </row>
     <row r="7" spans="1:11" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="H7" s="14"/>
       <c r="I7" s="14" t="s">
-        <v>30</v>
+        <v>137</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="K7" s="7"/>
     </row>
     <row r="8" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
       <c r="B8" s="11" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -1317,26 +1305,26 @@
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
       <c r="B9" s="13" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="14" t="s">
-        <v>33</v>
-      </c>
       <c r="F9" s="14" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="H9" s="14"/>
       <c r="I9" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
@@ -1344,84 +1332,84 @@
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="11" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="F10" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="G10" s="12" t="s">
         <v>36</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>37</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
     </row>
     <row r="11" spans="1:11" ht="229.5" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="F11" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="G11" s="14" t="s">
         <v>40</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>41</v>
       </c>
       <c r="H11" s="14"/>
       <c r="I11" s="14" t="s">
         <v>39</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="K11" s="7"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="11" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="F12" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="G12" s="12" t="s">
         <v>44</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>45</v>
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
@@ -1429,48 +1417,48 @@
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" s="14" t="s">
         <v>47</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>48</v>
       </c>
       <c r="H13" s="14"/>
       <c r="I13" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
     </row>
     <row r="14" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E14" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="G14" s="12" t="s">
         <v>51</v>
-      </c>
-      <c r="G14" s="12" t="s">
-        <v>52</v>
       </c>
       <c r="H14" s="12"/>
       <c r="I14" s="12" t="s">
@@ -1480,122 +1468,122 @@
     <row r="15" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10"/>
       <c r="B15" s="11" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="E15" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>61</v>
-      </c>
       <c r="G15" s="12" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10"/>
       <c r="B16" s="13" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H16" s="14"/>
       <c r="I16" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10"/>
       <c r="B17" s="11" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10"/>
       <c r="B18" s="11" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E18" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="G18" s="12" t="s">
         <v>61</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>62</v>
       </c>
       <c r="H18" s="12"/>
       <c r="I18" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10"/>
       <c r="B19" s="13" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H19" s="14" t="s">
         <v>47</v>
@@ -1607,426 +1595,424 @@
     <row r="20" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10"/>
       <c r="B20" s="13" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="H20" s="14"/>
       <c r="I20" s="14" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="12" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10"/>
       <c r="B22" s="13" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F22" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="G22" s="14" t="s">
         <v>120</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>124</v>
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="267.75" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E23" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F23" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="F23" s="12" t="s">
+      <c r="G23" s="12" t="s">
         <v>55</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>56</v>
       </c>
       <c r="H23" s="12"/>
       <c r="I23" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="102" x14ac:dyDescent="0.25">
       <c r="B24" s="13" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E24" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F24" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="G24" s="14" t="s">
         <v>58</v>
-      </c>
-      <c r="G24" s="14" t="s">
-        <v>59</v>
       </c>
       <c r="H24" s="14"/>
       <c r="I24" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B25" s="11" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E25" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F25" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="F25" s="12" t="s">
-        <v>61</v>
-      </c>
       <c r="G25" s="12" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B26" s="13" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H26" s="14"/>
       <c r="I26" s="14" t="s">
-        <v>63</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="H27" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="I27" s="14" t="s">
-        <v>89</v>
+        <v>62</v>
+      </c>
+      <c r="H27" s="14"/>
+      <c r="I27" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B28" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B29" s="13" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H29" s="14"/>
       <c r="I29" s="14" t="s">
-        <v>69</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B30" s="11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B31" s="11" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H31" s="12"/>
       <c r="I31" s="12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="178.5" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="G32" s="12" t="s">
         <v>74</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F32" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="G32" s="12" t="s">
-        <v>77</v>
       </c>
       <c r="H32" s="12"/>
       <c r="I32" s="12" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="B33" s="13" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H33" s="14"/>
       <c r="I33" s="14" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B34" s="11" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="G34" s="12" t="s">
         <v>80</v>
-      </c>
-      <c r="E34" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="F34" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="G34" s="12" t="s">
-        <v>83</v>
       </c>
       <c r="H34" s="12"/>
       <c r="I34" s="12" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B35" s="13" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H35" s="14"/>
       <c r="I35" s="14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B36" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H36" s="12"/>
       <c r="I36" s="12" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
